--- a/research/traditional_assets/database/data/hungary/hungary_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_construction_supplies.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09497029362174889</v>
+        <v>0.09492577035748932</v>
       </c>
       <c r="C2">
-        <v>110.0540819775007</v>
+        <v>109.189825504204</v>
       </c>
       <c r="D2">
-        <v>103.4340819775007</v>
+        <v>103.527825504204</v>
       </c>
       <c r="E2">
-        <v>-53.49999999999999</v>
+        <v>-52.54199999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9579999999999999</v>
       </c>
       <c r="G2">
         <v>6.62</v>
@@ -1439,28 +1439,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04818739999999999</v>
       </c>
       <c r="N2">
-        <v>8.080000000000002</v>
+        <v>8.031812600000002</v>
       </c>
       <c r="O2">
-        <v>0.7272000000000002</v>
+        <v>0.7228631340000001</v>
       </c>
       <c r="P2">
-        <v>7.352800000000002</v>
+        <v>7.308949466000002</v>
       </c>
       <c r="Q2">
-        <v>14.1728</v>
+        <v>14.128949466</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09497029362174889</v>
+        <v>0.09542226298736295</v>
       </c>
       <c r="T2">
-        <v>0.715487684377053</v>
+        <v>0.7220643893546602</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>167.6786877897542</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09492577035748932</v>
+        <v>0.09488124709322976</v>
       </c>
       <c r="C3">
-        <v>109.189825504204</v>
+        <v>108.3257391067738</v>
       </c>
       <c r="D3">
-        <v>103.527825504204</v>
+        <v>103.6217391067738</v>
       </c>
       <c r="E3">
-        <v>-52.54199999999999</v>
+        <v>-51.584</v>
       </c>
       <c r="F3">
-        <v>0.9579999999999999</v>
+        <v>1.916</v>
       </c>
       <c r="G3">
         <v>6.62</v>
@@ -1521,28 +1521,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M3">
-        <v>0.04818739999999999</v>
+        <v>0.09637479999999998</v>
       </c>
       <c r="N3">
-        <v>8.031812600000002</v>
+        <v>7.983625200000002</v>
       </c>
       <c r="O3">
-        <v>0.7228631340000001</v>
+        <v>0.7185262680000002</v>
       </c>
       <c r="P3">
-        <v>7.308949466000002</v>
+        <v>7.265098932000003</v>
       </c>
       <c r="Q3">
-        <v>14.128949466</v>
+        <v>14.085098932</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09542226298736295</v>
+        <v>0.09588345621758138</v>
       </c>
       <c r="T3">
-        <v>0.7220643893546602</v>
+        <v>0.7287753128011983</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>167.6786877897542</v>
+        <v>83.83934389487712</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09488124709322976</v>
+        <v>0.09483672382897017</v>
       </c>
       <c r="C4">
-        <v>108.3257391067738</v>
+        <v>107.461823248475</v>
       </c>
       <c r="D4">
-        <v>103.6217391067738</v>
+        <v>103.715823248475</v>
       </c>
       <c r="E4">
-        <v>-51.584</v>
+        <v>-50.62599999999999</v>
       </c>
       <c r="F4">
-        <v>1.916</v>
+        <v>2.873999999999999</v>
       </c>
       <c r="G4">
         <v>6.62</v>
@@ -1603,28 +1603,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M4">
-        <v>0.09637479999999998</v>
+        <v>0.1445621999999999</v>
       </c>
       <c r="N4">
-        <v>7.983625200000002</v>
+        <v>7.935437800000002</v>
       </c>
       <c r="O4">
-        <v>0.7185262680000002</v>
+        <v>0.7141894020000001</v>
       </c>
       <c r="P4">
-        <v>7.265098932000003</v>
+        <v>7.221248398000002</v>
       </c>
       <c r="Q4">
-        <v>14.085098932</v>
+        <v>14.041248398</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09588345621758138</v>
+        <v>0.09635415858656719</v>
       </c>
       <c r="T4">
-        <v>0.7287753128011983</v>
+        <v>0.7356246058033351</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>83.83934389487712</v>
+        <v>55.89289592991809</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09483672382897017</v>
+        <v>0.09479220056471059</v>
       </c>
       <c r="C5">
-        <v>107.461823248475</v>
+        <v>106.5980783942567</v>
       </c>
       <c r="D5">
-        <v>103.715823248475</v>
+        <v>103.8100783942567</v>
       </c>
       <c r="E5">
-        <v>-50.62599999999999</v>
+        <v>-49.66799999999999</v>
       </c>
       <c r="F5">
-        <v>2.873999999999999</v>
+        <v>3.831999999999999</v>
       </c>
       <c r="G5">
         <v>6.62</v>
@@ -1685,28 +1685,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M5">
-        <v>0.1445621999999999</v>
+        <v>0.1927496</v>
       </c>
       <c r="N5">
-        <v>7.935437800000002</v>
+        <v>7.887250400000002</v>
       </c>
       <c r="O5">
-        <v>0.7141894020000001</v>
+        <v>0.7098525360000001</v>
       </c>
       <c r="P5">
-        <v>7.221248398000002</v>
+        <v>7.177397864000001</v>
       </c>
       <c r="Q5">
-        <v>14.041248398</v>
+        <v>13.997397864</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09635415858656719</v>
+        <v>0.09683466725490687</v>
       </c>
       <c r="T5">
-        <v>0.7356246058033351</v>
+        <v>0.7426165924096829</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>55.89289592991809</v>
+        <v>41.91967194743856</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09479220056471059</v>
+        <v>0.09474767730045103</v>
       </c>
       <c r="C6">
-        <v>106.5980783942567</v>
+        <v>105.7345050107595</v>
       </c>
       <c r="D6">
-        <v>103.8100783942567</v>
+        <v>103.9045050107595</v>
       </c>
       <c r="E6">
-        <v>-49.66799999999999</v>
+        <v>-48.70999999999999</v>
       </c>
       <c r="F6">
-        <v>3.831999999999999</v>
+        <v>4.789999999999999</v>
       </c>
       <c r="G6">
         <v>6.62</v>
@@ -1767,28 +1767,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M6">
-        <v>0.1927496</v>
+        <v>0.240937</v>
       </c>
       <c r="N6">
-        <v>7.887250400000002</v>
+        <v>7.839063000000002</v>
       </c>
       <c r="O6">
-        <v>0.7098525360000001</v>
+        <v>0.7055156700000002</v>
       </c>
       <c r="P6">
-        <v>7.177397864000001</v>
+        <v>7.133547330000002</v>
       </c>
       <c r="Q6">
-        <v>13.997397864</v>
+        <v>13.95354733</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09683466725490687</v>
+        <v>0.09732529189521161</v>
       </c>
       <c r="T6">
-        <v>0.7426165924096829</v>
+        <v>0.7497557787340592</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>41.91967194743856</v>
+        <v>33.53573755795085</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09474767730045103</v>
+        <v>0.09470315403619145</v>
       </c>
       <c r="C7">
-        <v>105.7345050107595</v>
+        <v>104.8711035663236</v>
       </c>
       <c r="D7">
-        <v>103.9045050107595</v>
+        <v>103.9991035663236</v>
       </c>
       <c r="E7">
-        <v>-48.70999999999999</v>
+        <v>-47.752</v>
       </c>
       <c r="F7">
-        <v>4.789999999999999</v>
+        <v>5.747999999999999</v>
       </c>
       <c r="G7">
         <v>6.62</v>
@@ -1849,28 +1849,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M7">
-        <v>0.240937</v>
+        <v>0.2891243999999999</v>
       </c>
       <c r="N7">
-        <v>7.839063000000002</v>
+        <v>7.790875600000001</v>
       </c>
       <c r="O7">
-        <v>0.7055156700000002</v>
+        <v>0.7011788040000001</v>
       </c>
       <c r="P7">
-        <v>7.133547330000002</v>
+        <v>7.089696796000001</v>
       </c>
       <c r="Q7">
-        <v>13.95354733</v>
+        <v>13.909696796</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09732529189521161</v>
+        <v>0.09782635535765048</v>
       </c>
       <c r="T7">
-        <v>0.7497557787340592</v>
+        <v>0.7570468626398053</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.53573755795085</v>
+        <v>27.94644796495904</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09470315403619145</v>
+        <v>0.09465863077193187</v>
       </c>
       <c r="C8">
-        <v>104.8711035663236</v>
+        <v>104.0078745309963</v>
       </c>
       <c r="D8">
-        <v>103.9991035663236</v>
+        <v>104.0938745309963</v>
       </c>
       <c r="E8">
-        <v>-47.752</v>
+        <v>-46.794</v>
       </c>
       <c r="F8">
-        <v>5.747999999999998</v>
+        <v>6.705999999999998</v>
       </c>
       <c r="G8">
         <v>6.62</v>
@@ -1931,28 +1931,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M8">
-        <v>0.2891243999999999</v>
+        <v>0.3373117999999999</v>
       </c>
       <c r="N8">
-        <v>7.790875600000002</v>
+        <v>7.742688200000002</v>
       </c>
       <c r="O8">
-        <v>0.7011788040000002</v>
+        <v>0.6968419380000002</v>
       </c>
       <c r="P8">
-        <v>7.089696796000002</v>
+        <v>7.045846262000001</v>
       </c>
       <c r="Q8">
-        <v>13.909696796</v>
+        <v>13.865846262</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09782635535765048</v>
+        <v>0.09833819437842137</v>
       </c>
       <c r="T8">
-        <v>0.7570468626398053</v>
+        <v>0.7644947440489005</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.94644796495905</v>
+        <v>23.95409825567918</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09465863077193187</v>
+        <v>0.0946141075076723</v>
       </c>
       <c r="C9">
-        <v>104.0078745309963</v>
+        <v>103.1448183765397</v>
       </c>
       <c r="D9">
-        <v>104.0938745309963</v>
+        <v>104.1888183765397</v>
       </c>
       <c r="E9">
-        <v>-46.794</v>
+        <v>-45.83599999999999</v>
       </c>
       <c r="F9">
-        <v>6.706</v>
+        <v>7.663999999999999</v>
       </c>
       <c r="G9">
         <v>6.62</v>
@@ -2013,28 +2013,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M9">
-        <v>0.3373117999999999</v>
+        <v>0.3854991999999999</v>
       </c>
       <c r="N9">
-        <v>7.742688200000002</v>
+        <v>7.694500800000002</v>
       </c>
       <c r="O9">
-        <v>0.6968419380000002</v>
+        <v>0.6925050720000001</v>
       </c>
       <c r="P9">
-        <v>7.045846262000001</v>
+        <v>7.001995728000002</v>
       </c>
       <c r="Q9">
-        <v>13.865846262</v>
+        <v>13.821995728</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09833819437842138</v>
+        <v>0.09886116033442641</v>
       </c>
       <c r="T9">
-        <v>0.7644947440489007</v>
+        <v>0.7721045359234111</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.95409825567918</v>
+        <v>20.95983597371928</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0946141075076723</v>
+        <v>0.09456958424341275</v>
       </c>
       <c r="C10">
-        <v>103.1448183765397</v>
+        <v>102.2819355764386</v>
       </c>
       <c r="D10">
-        <v>104.1888183765397</v>
+        <v>104.2839355764386</v>
       </c>
       <c r="E10">
-        <v>-45.83599999999999</v>
+        <v>-44.87799999999999</v>
       </c>
       <c r="F10">
-        <v>7.663999999999999</v>
+        <v>8.621999999999998</v>
       </c>
       <c r="G10">
         <v>6.62</v>
@@ -2095,28 +2095,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M10">
-        <v>0.3854991999999999</v>
+        <v>0.4336865999999999</v>
       </c>
       <c r="N10">
-        <v>7.694500800000002</v>
+        <v>7.646313400000002</v>
       </c>
       <c r="O10">
-        <v>0.6925050720000001</v>
+        <v>0.6881682060000002</v>
       </c>
       <c r="P10">
-        <v>7.001995728000002</v>
+        <v>6.958145194000002</v>
       </c>
       <c r="Q10">
-        <v>13.821995728</v>
+        <v>13.778145194</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09886116033442641</v>
+        <v>0.0993956200477063</v>
       </c>
       <c r="T10">
-        <v>0.7721045359234111</v>
+        <v>0.7798815759709878</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.95983597371928</v>
+        <v>18.63096530997269</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09456958424341275</v>
+        <v>0.09452506097915314</v>
       </c>
       <c r="C11">
-        <v>102.2819355764386</v>
+        <v>101.4192266059088</v>
       </c>
       <c r="D11">
-        <v>104.2839355764386</v>
+        <v>104.3792266059088</v>
       </c>
       <c r="E11">
-        <v>-44.87799999999999</v>
+        <v>-43.91999999999999</v>
       </c>
       <c r="F11">
-        <v>8.621999999999998</v>
+        <v>9.579999999999998</v>
       </c>
       <c r="G11">
         <v>6.62</v>
@@ -2177,28 +2177,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M11">
-        <v>0.4336865999999999</v>
+        <v>0.4818739999999999</v>
       </c>
       <c r="N11">
-        <v>7.646313400000002</v>
+        <v>7.598126000000002</v>
       </c>
       <c r="O11">
-        <v>0.6881682060000002</v>
+        <v>0.6838313400000002</v>
       </c>
       <c r="P11">
-        <v>6.958145194000002</v>
+        <v>6.914294660000002</v>
       </c>
       <c r="Q11">
-        <v>13.778145194</v>
+        <v>13.73429466</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0993956200477063</v>
+        <v>0.0999419566435035</v>
       </c>
       <c r="T11">
-        <v>0.7798815759709878</v>
+        <v>0.7878314391307328</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.63096530997269</v>
+        <v>16.76786877897543</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09452506097915316</v>
+        <v>0.09448053771489358</v>
       </c>
       <c r="C12">
-        <v>101.4192266059088</v>
+        <v>100.5566919419041</v>
       </c>
       <c r="D12">
-        <v>104.3792266059088</v>
+        <v>104.4746919419041</v>
       </c>
       <c r="E12">
-        <v>-43.91999999999999</v>
+        <v>-42.962</v>
       </c>
       <c r="F12">
-        <v>9.579999999999998</v>
+        <v>10.538</v>
       </c>
       <c r="G12">
         <v>6.62</v>
@@ -2259,28 +2259,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M12">
-        <v>0.4818739999999999</v>
+        <v>0.5300613999999999</v>
       </c>
       <c r="N12">
-        <v>7.598126000000002</v>
+        <v>7.549938600000002</v>
       </c>
       <c r="O12">
-        <v>0.6838313400000002</v>
+        <v>0.6794944740000002</v>
       </c>
       <c r="P12">
-        <v>6.914294660000002</v>
+        <v>6.870444126000002</v>
       </c>
       <c r="Q12">
-        <v>13.73429466</v>
+        <v>13.690444126</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0999419566435035</v>
+        <v>0.1005005704661726</v>
       </c>
       <c r="T12">
-        <v>0.7878314391307328</v>
+        <v>0.7959599509008092</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.76786877897543</v>
+        <v>15.24351707179584</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09448053771489358</v>
+        <v>0.094436014450634</v>
       </c>
       <c r="C13">
-        <v>100.5566919419041</v>
+        <v>99.69433206312519</v>
       </c>
       <c r="D13">
-        <v>104.4746919419041</v>
+        <v>104.5703320631252</v>
       </c>
       <c r="E13">
-        <v>-42.962</v>
+        <v>-42.004</v>
       </c>
       <c r="F13">
-        <v>10.538</v>
+        <v>11.496</v>
       </c>
       <c r="G13">
         <v>6.62</v>
@@ -2341,28 +2341,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M13">
-        <v>0.5300613999999999</v>
+        <v>0.5782487999999998</v>
       </c>
       <c r="N13">
-        <v>7.549938600000002</v>
+        <v>7.501751200000002</v>
       </c>
       <c r="O13">
-        <v>0.6794944740000002</v>
+        <v>0.6751576080000001</v>
       </c>
       <c r="P13">
-        <v>6.870444126000002</v>
+        <v>6.826593592000002</v>
       </c>
       <c r="Q13">
-        <v>13.690444126</v>
+        <v>13.646593592</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1005005704661726</v>
+        <v>0.1010718800575386</v>
       </c>
       <c r="T13">
-        <v>0.7959599509008092</v>
+        <v>0.8042732015747509</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.24351707179584</v>
+        <v>13.97322398247952</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.094436014450634</v>
+        <v>0.09439149118637444</v>
       </c>
       <c r="C14">
-        <v>99.69433206312519</v>
+        <v>98.83214745002697</v>
       </c>
       <c r="D14">
-        <v>104.5703320631252</v>
+        <v>104.666147450027</v>
       </c>
       <c r="E14">
-        <v>-42.004</v>
+        <v>-41.04599999999999</v>
       </c>
       <c r="F14">
-        <v>11.496</v>
+        <v>12.454</v>
       </c>
       <c r="G14">
         <v>6.62</v>
@@ -2423,28 +2423,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M14">
-        <v>0.5782487999999998</v>
+        <v>0.6264361999999999</v>
       </c>
       <c r="N14">
-        <v>7.501751200000002</v>
+        <v>7.453563800000002</v>
       </c>
       <c r="O14">
-        <v>0.6751576080000001</v>
+        <v>0.6708207420000002</v>
       </c>
       <c r="P14">
-        <v>6.826593592000002</v>
+        <v>6.782743058000002</v>
       </c>
       <c r="Q14">
-        <v>13.646593592</v>
+        <v>13.602743058</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1010718800575386</v>
+        <v>0.1016563232027292</v>
       </c>
       <c r="T14">
-        <v>0.8042732015747509</v>
+        <v>0.8127775614595879</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>13.97322398247952</v>
+        <v>12.89836059921186</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09439149118637444</v>
+        <v>0.09453806792211486</v>
       </c>
       <c r="C15">
-        <v>98.83214745002697</v>
+        <v>97.55937046173381</v>
       </c>
       <c r="D15">
-        <v>104.666147450027</v>
+        <v>104.3513704617338</v>
       </c>
       <c r="E15">
-        <v>-41.04599999999999</v>
+        <v>-40.08799999999999</v>
       </c>
       <c r="F15">
-        <v>12.454</v>
+        <v>13.412</v>
       </c>
       <c r="G15">
         <v>6.62</v>
@@ -2505,45 +2505,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M15">
-        <v>0.6264361999999999</v>
+        <v>0.6947416</v>
       </c>
       <c r="N15">
-        <v>7.453563800000002</v>
+        <v>7.385258400000001</v>
       </c>
       <c r="O15">
-        <v>0.6708207420000002</v>
+        <v>0.6646732560000002</v>
       </c>
       <c r="P15">
-        <v>6.782743058000002</v>
+        <v>6.720585144000001</v>
       </c>
       <c r="Q15">
-        <v>13.602743058</v>
+        <v>13.540585144</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1016563232027292</v>
+        <v>0.1022543580489708</v>
       </c>
       <c r="T15">
-        <v>0.8127775614595879</v>
+        <v>0.8214796971557001</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.09</v>
       </c>
       <c r="W15">
-        <v>0.045773</v>
+        <v>0.047138</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>12.89836059921186</v>
+        <v>11.63022338089442</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09453806792211486</v>
+        <v>0.09450719465785529</v>
       </c>
       <c r="C16">
-        <v>97.55937046173381</v>
+        <v>96.66751402550798</v>
       </c>
       <c r="D16">
-        <v>104.3513704617338</v>
+        <v>104.417514025508</v>
       </c>
       <c r="E16">
-        <v>-40.08799999999999</v>
+        <v>-39.13</v>
       </c>
       <c r="F16">
-        <v>13.412</v>
+        <v>14.37</v>
       </c>
       <c r="G16">
         <v>6.62</v>
@@ -2587,28 +2587,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M16">
-        <v>0.6947416</v>
+        <v>0.744366</v>
       </c>
       <c r="N16">
-        <v>7.385258400000001</v>
+        <v>7.335634000000002</v>
       </c>
       <c r="O16">
-        <v>0.6646732560000002</v>
+        <v>0.6602070600000001</v>
       </c>
       <c r="P16">
-        <v>6.720585144000001</v>
+        <v>6.675426940000001</v>
       </c>
       <c r="Q16">
-        <v>13.540585144</v>
+        <v>13.49542694</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1022543580489708</v>
+        <v>0.1028664643033592</v>
       </c>
       <c r="T16">
-        <v>0.8214796971557001</v>
+        <v>0.8303865889858386</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.63022338089442</v>
+        <v>10.85487515550146</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09450719465785529</v>
+        <v>0.09447632139359571</v>
       </c>
       <c r="C17">
-        <v>96.66751402550798</v>
+        <v>95.7757414932283</v>
       </c>
       <c r="D17">
-        <v>104.417514025508</v>
+        <v>104.4837414932283</v>
       </c>
       <c r="E17">
-        <v>-39.13</v>
+        <v>-38.172</v>
       </c>
       <c r="F17">
-        <v>14.37</v>
+        <v>15.328</v>
       </c>
       <c r="G17">
         <v>6.62</v>
@@ -2669,28 +2669,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M17">
-        <v>0.7443659999999999</v>
+        <v>0.7939903999999999</v>
       </c>
       <c r="N17">
-        <v>7.335634000000002</v>
+        <v>7.286009600000002</v>
       </c>
       <c r="O17">
-        <v>0.6602070600000002</v>
+        <v>0.6557408640000001</v>
       </c>
       <c r="P17">
-        <v>6.675426940000002</v>
+        <v>6.630268736000001</v>
       </c>
       <c r="Q17">
-        <v>13.49542694</v>
+        <v>13.450268736</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1028664643033592</v>
+        <v>0.1034931445161854</v>
       </c>
       <c r="T17">
-        <v>0.8303865889858386</v>
+        <v>0.8395055496690755</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.85487515550147</v>
+        <v>10.17644545828262</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09447632139359571</v>
+        <v>0.09470843812933613</v>
       </c>
       <c r="C18">
-        <v>95.7757414932283</v>
+        <v>94.32186744897402</v>
       </c>
       <c r="D18">
-        <v>104.4837414932283</v>
+        <v>103.987867448974</v>
       </c>
       <c r="E18">
-        <v>-38.172</v>
+        <v>-37.214</v>
       </c>
       <c r="F18">
-        <v>15.328</v>
+        <v>16.286</v>
       </c>
       <c r="G18">
         <v>6.62</v>
@@ -2751,45 +2751,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M18">
-        <v>0.7939903999999999</v>
+        <v>0.8713009999999999</v>
       </c>
       <c r="N18">
-        <v>7.286009600000002</v>
+        <v>7.208699000000002</v>
       </c>
       <c r="O18">
-        <v>0.6557408640000001</v>
+        <v>0.6487829100000001</v>
       </c>
       <c r="P18">
-        <v>6.630268736000001</v>
+        <v>6.559916090000002</v>
       </c>
       <c r="Q18">
-        <v>13.450268736</v>
+        <v>13.37991609</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1034931445161854</v>
+        <v>0.1041349254570315</v>
       </c>
       <c r="T18">
-        <v>0.8395055496690755</v>
+        <v>0.8488442443446796</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.09</v>
       </c>
       <c r="W18">
-        <v>0.047138</v>
+        <v>0.048685</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.17644545828262</v>
+        <v>9.273488725480636</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09470843812933613</v>
+        <v>0.09469303486507655</v>
       </c>
       <c r="C19">
-        <v>94.32186744897402</v>
+        <v>93.39662779217069</v>
       </c>
       <c r="D19">
-        <v>103.987867448974</v>
+        <v>104.0206277921707</v>
       </c>
       <c r="E19">
-        <v>-37.214</v>
+        <v>-36.25599999999999</v>
       </c>
       <c r="F19">
-        <v>16.286</v>
+        <v>17.244</v>
       </c>
       <c r="G19">
         <v>6.62</v>
@@ -2833,28 +2833,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M19">
-        <v>0.8713009999999999</v>
+        <v>0.922554</v>
       </c>
       <c r="N19">
-        <v>7.208699000000002</v>
+        <v>7.157446000000002</v>
       </c>
       <c r="O19">
-        <v>0.6487829100000001</v>
+        <v>0.6441701400000002</v>
       </c>
       <c r="P19">
-        <v>6.559916090000002</v>
+        <v>6.513275860000002</v>
       </c>
       <c r="Q19">
-        <v>13.37991609</v>
+        <v>13.33327586</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1041349254570315</v>
+        <v>0.1047923595915568</v>
       </c>
       <c r="T19">
-        <v>0.8488442443446796</v>
+        <v>0.8584107120611522</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.273488725480636</v>
+        <v>8.758294907398376</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09469303486507656</v>
+        <v>0.09467763160081699</v>
       </c>
       <c r="C20">
-        <v>93.39662779217068</v>
+        <v>92.47140878351277</v>
       </c>
       <c r="D20">
-        <v>104.0206277921707</v>
+        <v>104.0534087835128</v>
       </c>
       <c r="E20">
-        <v>-36.256</v>
+        <v>-35.29799999999999</v>
       </c>
       <c r="F20">
-        <v>17.244</v>
+        <v>18.202</v>
       </c>
       <c r="G20">
         <v>6.62</v>
@@ -2915,28 +2915,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M20">
-        <v>0.9225539999999998</v>
+        <v>0.9738069999999999</v>
       </c>
       <c r="N20">
-        <v>7.157446000000002</v>
+        <v>7.106193000000002</v>
       </c>
       <c r="O20">
-        <v>0.6441701400000002</v>
+        <v>0.6395573700000001</v>
       </c>
       <c r="P20">
-        <v>6.513275860000002</v>
+        <v>6.466635630000002</v>
       </c>
       <c r="Q20">
-        <v>13.33327586</v>
+        <v>13.28663563</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1047923595915568</v>
+        <v>0.1054660266676753</v>
       </c>
       <c r="T20">
-        <v>0.8584107120611522</v>
+        <v>0.8682133888570437</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.75829490739838</v>
+        <v>8.297332017535306</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09467763160081699</v>
+        <v>0.09466222833655741</v>
       </c>
       <c r="C21">
-        <v>92.47140878351277</v>
+        <v>91.54621044252765</v>
       </c>
       <c r="D21">
-        <v>104.0534087835128</v>
+        <v>104.0862104425276</v>
       </c>
       <c r="E21">
-        <v>-35.29799999999999</v>
+        <v>-34.34</v>
       </c>
       <c r="F21">
-        <v>18.202</v>
+        <v>19.16</v>
       </c>
       <c r="G21">
         <v>6.62</v>
@@ -2997,28 +2997,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M21">
-        <v>0.9738069999999999</v>
+        <v>1.02506</v>
       </c>
       <c r="N21">
-        <v>7.106193000000002</v>
+        <v>7.054940000000002</v>
       </c>
       <c r="O21">
-        <v>0.6395573700000001</v>
+        <v>0.6349446000000002</v>
       </c>
       <c r="P21">
-        <v>6.466635630000002</v>
+        <v>6.419995400000002</v>
       </c>
       <c r="Q21">
-        <v>13.28663563</v>
+        <v>13.2399954</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1054660266676753</v>
+        <v>0.1061565354206968</v>
       </c>
       <c r="T21">
-        <v>0.8682133888570437</v>
+        <v>0.8782611325728326</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.297332017535306</v>
+        <v>7.88246541665854</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09466222833655741</v>
+        <v>0.09479970507229785</v>
       </c>
       <c r="C22">
-        <v>91.54621044252765</v>
+        <v>90.29617945119581</v>
       </c>
       <c r="D22">
-        <v>104.0862104425276</v>
+        <v>103.7941794511958</v>
       </c>
       <c r="E22">
-        <v>-34.34</v>
+        <v>-33.38199999999999</v>
       </c>
       <c r="F22">
-        <v>19.16</v>
+        <v>20.118</v>
       </c>
       <c r="G22">
         <v>6.62</v>
@@ -3079,45 +3079,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M22">
-        <v>1.02506</v>
+        <v>1.0924074</v>
       </c>
       <c r="N22">
-        <v>7.054940000000002</v>
+        <v>6.987592600000002</v>
       </c>
       <c r="O22">
-        <v>0.6349446000000002</v>
+        <v>0.6288833340000002</v>
       </c>
       <c r="P22">
-        <v>6.419995400000002</v>
+        <v>6.358709266000002</v>
       </c>
       <c r="Q22">
-        <v>13.2399954</v>
+        <v>13.178709266</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1061565354206968</v>
+        <v>0.1068645254079719</v>
       </c>
       <c r="T22">
-        <v>0.8782611325728326</v>
+        <v>0.888563249547249</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.09</v>
       </c>
       <c r="W22">
-        <v>0.048685</v>
+        <v>0.04941300000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.88246541665854</v>
+        <v>7.396507932846301</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09479970507229785</v>
+        <v>0.09479158180803826</v>
       </c>
       <c r="C23">
-        <v>90.29617945119581</v>
+        <v>89.35538950070172</v>
       </c>
       <c r="D23">
-        <v>103.7941794511958</v>
+        <v>103.8113895007017</v>
       </c>
       <c r="E23">
-        <v>-33.382</v>
+        <v>-32.42399999999999</v>
       </c>
       <c r="F23">
-        <v>20.11799999999999</v>
+        <v>21.076</v>
       </c>
       <c r="G23">
         <v>6.62</v>
@@ -3161,28 +3161,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M23">
-        <v>1.0924074</v>
+        <v>1.1444268</v>
       </c>
       <c r="N23">
-        <v>6.987592600000002</v>
+        <v>6.935573200000002</v>
       </c>
       <c r="O23">
-        <v>0.6288833340000002</v>
+        <v>0.6242015880000001</v>
       </c>
       <c r="P23">
-        <v>6.358709266000002</v>
+        <v>6.311371612000002</v>
       </c>
       <c r="Q23">
-        <v>13.178709266</v>
+        <v>13.131371612</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1068645254079719</v>
+        <v>0.1075906689846644</v>
       </c>
       <c r="T23">
-        <v>0.888563249547249</v>
+        <v>0.8991295233671632</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.396507932846302</v>
+        <v>7.060303026807833</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09479158180803826</v>
+        <v>0.0947834585437787</v>
       </c>
       <c r="C24">
-        <v>89.35538950070172</v>
+        <v>88.41460525832963</v>
       </c>
       <c r="D24">
-        <v>103.8113895007017</v>
+        <v>103.8286052583296</v>
       </c>
       <c r="E24">
-        <v>-32.42399999999999</v>
+        <v>-31.466</v>
       </c>
       <c r="F24">
-        <v>21.076</v>
+        <v>22.034</v>
       </c>
       <c r="G24">
         <v>6.62</v>
@@ -3243,28 +3243,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M24">
-        <v>1.1444268</v>
+        <v>1.1964462</v>
       </c>
       <c r="N24">
-        <v>6.935573200000002</v>
+        <v>6.883553800000002</v>
       </c>
       <c r="O24">
-        <v>0.6242015880000001</v>
+        <v>0.6195198420000002</v>
       </c>
       <c r="P24">
-        <v>6.311371612000002</v>
+        <v>6.264033958000002</v>
       </c>
       <c r="Q24">
-        <v>13.131371612</v>
+        <v>13.084033958</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1075906689846644</v>
+        <v>0.1083356734334788</v>
       </c>
       <c r="T24">
-        <v>0.8991295233671632</v>
+        <v>0.9099702458577247</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.060303026807833</v>
+        <v>6.753333329990101</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0947834585437787</v>
+        <v>0.09477533527951912</v>
       </c>
       <c r="C25">
-        <v>88.41460525832963</v>
+        <v>87.47382672691998</v>
       </c>
       <c r="D25">
-        <v>103.8286052583296</v>
+        <v>103.84582672692</v>
       </c>
       <c r="E25">
-        <v>-31.466</v>
+        <v>-30.508</v>
       </c>
       <c r="F25">
-        <v>22.034</v>
+        <v>22.992</v>
       </c>
       <c r="G25">
         <v>6.62</v>
@@ -3325,28 +3325,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M25">
-        <v>1.1964462</v>
+        <v>1.2484656</v>
       </c>
       <c r="N25">
-        <v>6.883553800000002</v>
+        <v>6.831534400000002</v>
       </c>
       <c r="O25">
-        <v>0.6195198420000002</v>
+        <v>0.6148380960000002</v>
       </c>
       <c r="P25">
-        <v>6.264033958000002</v>
+        <v>6.216696304000003</v>
       </c>
       <c r="Q25">
-        <v>13.084033958</v>
+        <v>13.036696304</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1083356734334788</v>
+        <v>0.1091002832625252</v>
       </c>
       <c r="T25">
-        <v>0.9099702458577247</v>
+        <v>0.9210962505190905</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.753333329990101</v>
+        <v>6.471944441240514</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09477533527951912</v>
+        <v>0.09476721201525955</v>
       </c>
       <c r="C26">
-        <v>87.47382672691998</v>
+        <v>86.53305390931484</v>
       </c>
       <c r="D26">
-        <v>103.84582672692</v>
+        <v>103.8630539093148</v>
       </c>
       <c r="E26">
-        <v>-30.508</v>
+        <v>-29.55</v>
       </c>
       <c r="F26">
-        <v>22.99199999999999</v>
+        <v>23.95</v>
       </c>
       <c r="G26">
         <v>6.62</v>
@@ -3407,28 +3407,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M26">
-        <v>1.2484656</v>
+        <v>1.300485</v>
       </c>
       <c r="N26">
-        <v>6.831534400000002</v>
+        <v>6.779515000000002</v>
       </c>
       <c r="O26">
-        <v>0.6148380960000002</v>
+        <v>0.6101563500000001</v>
       </c>
       <c r="P26">
-        <v>6.216696304000003</v>
+        <v>6.169358650000001</v>
       </c>
       <c r="Q26">
-        <v>13.036696304</v>
+        <v>12.98935865</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1091002832625252</v>
+        <v>0.1098852826870127</v>
       </c>
       <c r="T26">
-        <v>0.9210962505190903</v>
+        <v>0.9325189486380924</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.471944441240515</v>
+        <v>6.213066663590893</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09476721201525955</v>
+        <v>0.09499568875099998</v>
       </c>
       <c r="C27">
-        <v>86.53305390931484</v>
+        <v>85.09268864268871</v>
       </c>
       <c r="D27">
-        <v>103.8630539093148</v>
+        <v>103.3806886426887</v>
       </c>
       <c r="E27">
-        <v>-29.55</v>
+        <v>-28.592</v>
       </c>
       <c r="F27">
-        <v>23.95</v>
+        <v>24.908</v>
       </c>
       <c r="G27">
         <v>6.62</v>
@@ -3489,45 +3489,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M27">
-        <v>1.300485</v>
+        <v>1.3774124</v>
       </c>
       <c r="N27">
-        <v>6.779515000000002</v>
+        <v>6.702587600000002</v>
       </c>
       <c r="O27">
-        <v>0.6101563500000001</v>
+        <v>0.6032328840000002</v>
       </c>
       <c r="P27">
-        <v>6.169358650000001</v>
+        <v>6.099354716000001</v>
       </c>
       <c r="Q27">
-        <v>12.98935865</v>
+        <v>12.919354716</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1098852826870127</v>
+        <v>0.1106914983121621</v>
       </c>
       <c r="T27">
-        <v>0.9325189486380924</v>
+        <v>0.9442503683278783</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.09</v>
       </c>
       <c r="W27">
-        <v>0.04941300000000001</v>
+        <v>0.05032300000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.213066663590893</v>
+        <v>5.866071773420947</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09499568875099998</v>
+        <v>0.09499666548674039</v>
       </c>
       <c r="C28">
-        <v>85.09268864268871</v>
+        <v>84.13263615371478</v>
       </c>
       <c r="D28">
-        <v>103.3806886426887</v>
+        <v>103.3786361537148</v>
       </c>
       <c r="E28">
-        <v>-28.592</v>
+        <v>-27.634</v>
       </c>
       <c r="F28">
-        <v>24.908</v>
+        <v>25.866</v>
       </c>
       <c r="G28">
         <v>6.62</v>
@@ -3571,28 +3571,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M28">
-        <v>1.3774124</v>
+        <v>1.4303898</v>
       </c>
       <c r="N28">
-        <v>6.702587600000002</v>
+        <v>6.649610200000001</v>
       </c>
       <c r="O28">
-        <v>0.6032328840000002</v>
+        <v>0.5984649180000001</v>
       </c>
       <c r="P28">
-        <v>6.099354716000001</v>
+        <v>6.051145282000001</v>
       </c>
       <c r="Q28">
-        <v>12.919354716</v>
+        <v>12.871145282</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1106914983121621</v>
+        <v>0.1115198020366307</v>
       </c>
       <c r="T28">
-        <v>0.9442503683278783</v>
+        <v>0.9563031967762885</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.866071773420947</v>
+        <v>5.648809855886837</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09499666548674039</v>
+        <v>0.09499764222248083</v>
       </c>
       <c r="C29">
-        <v>84.13263615371478</v>
+        <v>83.17258374623817</v>
       </c>
       <c r="D29">
-        <v>103.3786361537148</v>
+        <v>103.3765837462382</v>
       </c>
       <c r="E29">
-        <v>-27.634</v>
+        <v>-26.67599999999999</v>
       </c>
       <c r="F29">
-        <v>25.866</v>
+        <v>26.824</v>
       </c>
       <c r="G29">
         <v>6.62</v>
@@ -3653,28 +3653,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M29">
-        <v>1.4303898</v>
+        <v>1.4833672</v>
       </c>
       <c r="N29">
-        <v>6.649610200000001</v>
+        <v>6.596632800000002</v>
       </c>
       <c r="O29">
-        <v>0.5984649180000001</v>
+        <v>0.5936969520000002</v>
       </c>
       <c r="P29">
-        <v>6.051145282000001</v>
+        <v>6.002935848000002</v>
       </c>
       <c r="Q29">
-        <v>12.871145282</v>
+        <v>12.822935848</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1115198020366307</v>
+        <v>0.11237111419789</v>
       </c>
       <c r="T29">
-        <v>0.9563031967762885</v>
+        <v>0.9686908260149324</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.648809855886837</v>
+        <v>5.447066646748022</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09499764222248083</v>
+        <v>0.09499861895822125</v>
       </c>
       <c r="C30">
-        <v>83.17258374623817</v>
+        <v>82.21253142025412</v>
       </c>
       <c r="D30">
-        <v>103.3765837462382</v>
+        <v>103.3745314202541</v>
       </c>
       <c r="E30">
-        <v>-26.67599999999999</v>
+        <v>-25.71799999999999</v>
       </c>
       <c r="F30">
-        <v>26.824</v>
+        <v>27.782</v>
       </c>
       <c r="G30">
         <v>6.62</v>
@@ -3735,28 +3735,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M30">
-        <v>1.4833672</v>
+        <v>1.5363446</v>
       </c>
       <c r="N30">
-        <v>6.596632800000002</v>
+        <v>6.543655400000002</v>
       </c>
       <c r="O30">
-        <v>0.5936969520000002</v>
+        <v>0.5889289860000002</v>
       </c>
       <c r="P30">
-        <v>6.002935848000002</v>
+        <v>5.954726414000002</v>
       </c>
       <c r="Q30">
-        <v>12.822935848</v>
+        <v>12.774726414</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.11237111419789</v>
+        <v>0.1132464069834102</v>
       </c>
       <c r="T30">
-        <v>0.9686908260149324</v>
+        <v>0.9814274025560732</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.447066646748022</v>
+        <v>5.2592367623774</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09499861895822125</v>
+        <v>0.09499959569396167</v>
       </c>
       <c r="C31">
-        <v>82.21253142025412</v>
+        <v>81.25247917575773</v>
       </c>
       <c r="D31">
-        <v>103.3745314202541</v>
+        <v>103.3724791757577</v>
       </c>
       <c r="E31">
-        <v>-25.718</v>
+        <v>-24.76</v>
       </c>
       <c r="F31">
-        <v>27.78199999999999</v>
+        <v>28.73999999999999</v>
       </c>
       <c r="G31">
         <v>6.62</v>
@@ -3817,28 +3817,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M31">
-        <v>1.5363446</v>
+        <v>1.589322</v>
       </c>
       <c r="N31">
-        <v>6.543655400000002</v>
+        <v>6.490678000000003</v>
       </c>
       <c r="O31">
-        <v>0.5889289860000002</v>
+        <v>0.5841610200000003</v>
       </c>
       <c r="P31">
-        <v>5.954726414000002</v>
+        <v>5.906516980000003</v>
       </c>
       <c r="Q31">
-        <v>12.774726414</v>
+        <v>12.72651698</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1132464069834102</v>
+        <v>0.114146708134231</v>
       </c>
       <c r="T31">
-        <v>0.9814274025560731</v>
+        <v>0.9945278812841037</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.259236762377402</v>
+        <v>5.083928870298155</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09499959569396167</v>
+        <v>0.0950005724297021</v>
       </c>
       <c r="C32">
-        <v>81.25247917575773</v>
+        <v>80.29242701274414</v>
       </c>
       <c r="D32">
-        <v>103.3724791757577</v>
+        <v>103.3704270127441</v>
       </c>
       <c r="E32">
-        <v>-24.76</v>
+        <v>-23.802</v>
       </c>
       <c r="F32">
-        <v>28.73999999999999</v>
+        <v>29.69799999999999</v>
       </c>
       <c r="G32">
         <v>6.62</v>
@@ -3899,28 +3899,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M32">
-        <v>1.589322</v>
+        <v>1.6422994</v>
       </c>
       <c r="N32">
-        <v>6.490678000000003</v>
+        <v>6.437700600000002</v>
       </c>
       <c r="O32">
-        <v>0.5841610200000003</v>
+        <v>0.5793930540000002</v>
       </c>
       <c r="P32">
-        <v>5.906516980000003</v>
+        <v>5.858307546000002</v>
       </c>
       <c r="Q32">
-        <v>12.72651698</v>
+        <v>12.678307546</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.114146708134231</v>
+        <v>0.1150731049705828</v>
       </c>
       <c r="T32">
-        <v>0.9945278812841037</v>
+        <v>1.008008084033237</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.083928870298155</v>
+        <v>4.919931164804666</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0950005724297021</v>
+        <v>0.09500154916544254</v>
       </c>
       <c r="C33">
-        <v>80.29242701274414</v>
+        <v>79.33237493120851</v>
       </c>
       <c r="D33">
-        <v>103.3704270127441</v>
+        <v>103.3683749312085</v>
       </c>
       <c r="E33">
-        <v>-23.802</v>
+        <v>-22.844</v>
       </c>
       <c r="F33">
-        <v>29.69799999999999</v>
+        <v>30.656</v>
       </c>
       <c r="G33">
         <v>6.62</v>
@@ -3981,28 +3981,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M33">
-        <v>1.6422994</v>
+        <v>1.6952768</v>
       </c>
       <c r="N33">
-        <v>6.437700600000002</v>
+        <v>6.384723200000002</v>
       </c>
       <c r="O33">
-        <v>0.5793930540000002</v>
+        <v>0.5746250880000001</v>
       </c>
       <c r="P33">
-        <v>5.858307546000002</v>
+        <v>5.810098112000001</v>
       </c>
       <c r="Q33">
-        <v>12.678307546</v>
+        <v>12.630098112</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1150731049705828</v>
+        <v>0.1160267487727096</v>
       </c>
       <c r="T33">
-        <v>1.008008084033237</v>
+        <v>1.021884763333815</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.919931164804666</v>
+        <v>4.766183315904519</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09500154916544254</v>
+        <v>0.09500252590118295</v>
       </c>
       <c r="C34">
-        <v>79.33237493120851</v>
+        <v>78.37232293114602</v>
       </c>
       <c r="D34">
-        <v>103.3683749312085</v>
+        <v>103.366322931146</v>
       </c>
       <c r="E34">
-        <v>-22.844</v>
+        <v>-21.886</v>
       </c>
       <c r="F34">
-        <v>30.656</v>
+        <v>31.614</v>
       </c>
       <c r="G34">
         <v>6.62</v>
@@ -4063,28 +4063,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M34">
-        <v>1.6952768</v>
+        <v>1.7482542</v>
       </c>
       <c r="N34">
-        <v>6.384723200000002</v>
+        <v>6.331745800000002</v>
       </c>
       <c r="O34">
-        <v>0.5746250880000001</v>
+        <v>0.5698571220000002</v>
       </c>
       <c r="P34">
-        <v>5.810098112000001</v>
+        <v>5.761888678000002</v>
       </c>
       <c r="Q34">
-        <v>12.630098112</v>
+        <v>12.581888678</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1160267487727096</v>
+        <v>0.1170088595540044</v>
       </c>
       <c r="T34">
-        <v>1.021884763333815</v>
+        <v>1.036175671867246</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.766183315904519</v>
+        <v>4.621753518452867</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09500252590118295</v>
+        <v>0.09577700263692338</v>
       </c>
       <c r="C35">
-        <v>78.37232293114602</v>
+        <v>75.81248992505735</v>
       </c>
       <c r="D35">
-        <v>103.366322931146</v>
+        <v>101.7644899250573</v>
       </c>
       <c r="E35">
-        <v>-21.886</v>
+        <v>-20.928</v>
       </c>
       <c r="F35">
-        <v>31.614</v>
+        <v>32.572</v>
       </c>
       <c r="G35">
         <v>6.62</v>
@@ -4145,45 +4145,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M35">
-        <v>1.7482542</v>
+        <v>1.8826616</v>
       </c>
       <c r="N35">
-        <v>6.331745800000002</v>
+        <v>6.197338400000002</v>
       </c>
       <c r="O35">
-        <v>0.5698571220000002</v>
+        <v>0.5577604560000001</v>
       </c>
       <c r="P35">
-        <v>5.761888678000002</v>
+        <v>5.639577944000002</v>
       </c>
       <c r="Q35">
-        <v>12.581888678</v>
+        <v>12.459577944</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1170088595540044</v>
+        <v>0.1180207312680657</v>
       </c>
       <c r="T35">
-        <v>1.036175671867246</v>
+        <v>1.050899638235023</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.09</v>
       </c>
       <c r="W35">
-        <v>0.05032300000000001</v>
+        <v>0.05259800000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.621753518452867</v>
+        <v>4.291796252709464</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09577700263692338</v>
+        <v>0.0958007293726638</v>
       </c>
       <c r="C36">
-        <v>75.81248992505735</v>
+        <v>74.80619984628237</v>
       </c>
       <c r="D36">
-        <v>101.7644899250573</v>
+        <v>101.7161998462824</v>
       </c>
       <c r="E36">
-        <v>-20.928</v>
+        <v>-19.97</v>
       </c>
       <c r="F36">
-        <v>32.572</v>
+        <v>33.52999999999999</v>
       </c>
       <c r="G36">
         <v>6.62</v>
@@ -4227,28 +4227,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M36">
-        <v>1.8826616</v>
+        <v>1.938034</v>
       </c>
       <c r="N36">
-        <v>6.197338400000002</v>
+        <v>6.141966000000002</v>
       </c>
       <c r="O36">
-        <v>0.5577604560000001</v>
+        <v>0.5527769400000001</v>
       </c>
       <c r="P36">
-        <v>5.639577944000002</v>
+        <v>5.589189060000002</v>
       </c>
       <c r="Q36">
-        <v>12.459577944</v>
+        <v>12.40918906</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1180207312680657</v>
+        <v>0.1190637374964059</v>
       </c>
       <c r="T36">
-        <v>1.050899638235023</v>
+        <v>1.066076649721809</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.291796252709464</v>
+        <v>4.16917350263205</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0958007293726638</v>
+        <v>0.09582445610840423</v>
       </c>
       <c r="C37">
-        <v>74.80619984628237</v>
+        <v>73.79995557573911</v>
       </c>
       <c r="D37">
-        <v>101.7161998462824</v>
+        <v>101.6679555757391</v>
       </c>
       <c r="E37">
-        <v>-19.97</v>
+        <v>-19.01199999999999</v>
       </c>
       <c r="F37">
-        <v>33.52999999999999</v>
+        <v>34.488</v>
       </c>
       <c r="G37">
         <v>6.62</v>
@@ -4309,28 +4309,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M37">
-        <v>1.938034</v>
+        <v>1.9934064</v>
       </c>
       <c r="N37">
-        <v>6.141966000000002</v>
+        <v>6.086593600000002</v>
       </c>
       <c r="O37">
-        <v>0.5527769400000001</v>
+        <v>0.5477934240000002</v>
       </c>
       <c r="P37">
-        <v>5.589189060000002</v>
+        <v>5.538800176000002</v>
       </c>
       <c r="Q37">
-        <v>12.40918906</v>
+        <v>12.358800176</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1190637374964059</v>
+        <v>0.1201393376693816</v>
       </c>
       <c r="T37">
-        <v>1.066076649721809</v>
+        <v>1.081727942817557</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.16917350263205</v>
+        <v>4.053363127558937</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09582445610840423</v>
+        <v>0.09702663284414467</v>
       </c>
       <c r="C38">
-        <v>73.79995557573912</v>
+        <v>70.45603161045909</v>
       </c>
       <c r="D38">
-        <v>101.6679555757391</v>
+        <v>99.28203161045909</v>
       </c>
       <c r="E38">
-        <v>-19.012</v>
+        <v>-18.054</v>
       </c>
       <c r="F38">
-        <v>34.48799999999999</v>
+        <v>35.44599999999999</v>
       </c>
       <c r="G38">
         <v>6.62</v>
@@ -4391,45 +4391,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M38">
-        <v>1.9934064</v>
+        <v>2.172839799999999</v>
       </c>
       <c r="N38">
-        <v>6.086593600000002</v>
+        <v>5.907160200000003</v>
       </c>
       <c r="O38">
-        <v>0.5477934240000002</v>
+        <v>0.5316444180000002</v>
       </c>
       <c r="P38">
-        <v>5.538800176000002</v>
+        <v>5.375515782000003</v>
       </c>
       <c r="Q38">
-        <v>12.358800176</v>
+        <v>12.195515782</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1201393376693816</v>
+        <v>0.1212490838795947</v>
       </c>
       <c r="T38">
-        <v>1.081727942817557</v>
+        <v>1.097876102360789</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.09</v>
       </c>
       <c r="W38">
-        <v>0.05259800000000001</v>
+        <v>0.055783</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.053363127558938</v>
+        <v>3.71863586077538</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09702663284414467</v>
+        <v>0.09708220957988509</v>
       </c>
       <c r="C39">
-        <v>70.45603161045909</v>
+        <v>69.39043540351345</v>
       </c>
       <c r="D39">
-        <v>99.28203161045909</v>
+        <v>99.17443540351344</v>
       </c>
       <c r="E39">
-        <v>-18.054</v>
+        <v>-17.096</v>
       </c>
       <c r="F39">
-        <v>35.44599999999999</v>
+        <v>36.404</v>
       </c>
       <c r="G39">
         <v>6.62</v>
@@ -4473,28 +4473,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M39">
-        <v>2.172839799999999</v>
+        <v>2.2315652</v>
       </c>
       <c r="N39">
-        <v>5.907160200000003</v>
+        <v>5.848434800000001</v>
       </c>
       <c r="O39">
-        <v>0.5316444180000002</v>
+        <v>0.5263591320000001</v>
       </c>
       <c r="P39">
-        <v>5.375515782000003</v>
+        <v>5.322075668000002</v>
       </c>
       <c r="Q39">
-        <v>12.195515782</v>
+        <v>12.142075668</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1212490838795947</v>
+        <v>0.1223946283546534</v>
       </c>
       <c r="T39">
-        <v>1.097876102360789</v>
+        <v>1.114545170276384</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.71863586077538</v>
+        <v>3.620777022333921</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09708220957988509</v>
+        <v>0.09713778631562552</v>
       </c>
       <c r="C40">
-        <v>69.39043540351345</v>
+        <v>68.32507215737073</v>
       </c>
       <c r="D40">
-        <v>99.17443540351344</v>
+        <v>99.06707215737072</v>
       </c>
       <c r="E40">
-        <v>-17.096</v>
+        <v>-16.138</v>
       </c>
       <c r="F40">
-        <v>36.404</v>
+        <v>37.36199999999999</v>
       </c>
       <c r="G40">
         <v>6.62</v>
@@ -4555,28 +4555,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M40">
-        <v>2.2315652</v>
+        <v>2.2902906</v>
       </c>
       <c r="N40">
-        <v>5.848434800000001</v>
+        <v>5.789709400000002</v>
       </c>
       <c r="O40">
-        <v>0.5263591320000001</v>
+        <v>0.5210738460000002</v>
       </c>
       <c r="P40">
-        <v>5.322075668000002</v>
+        <v>5.268635554000002</v>
       </c>
       <c r="Q40">
-        <v>12.142075668</v>
+        <v>12.088635554</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1223946283546534</v>
+        <v>0.1235777316649599</v>
       </c>
       <c r="T40">
-        <v>1.114545170276384</v>
+        <v>1.131760765008883</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.620777022333921</v>
+        <v>3.527936585863821</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09713778631562552</v>
+        <v>0.09821256305136594</v>
       </c>
       <c r="C41">
-        <v>68.32507215737073</v>
+        <v>65.33559385839285</v>
       </c>
       <c r="D41">
-        <v>99.06707215737072</v>
+        <v>97.03559385839284</v>
       </c>
       <c r="E41">
-        <v>-16.138</v>
+        <v>-15.18</v>
       </c>
       <c r="F41">
-        <v>37.36199999999999</v>
+        <v>38.31999999999999</v>
       </c>
       <c r="G41">
         <v>6.62</v>
@@ -4637,45 +4637,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M41">
-        <v>2.2902906</v>
+        <v>2.456312</v>
       </c>
       <c r="N41">
-        <v>5.789709400000002</v>
+        <v>5.623688000000002</v>
       </c>
       <c r="O41">
-        <v>0.5210738460000002</v>
+        <v>0.5061319200000002</v>
       </c>
       <c r="P41">
-        <v>5.268635554000002</v>
+        <v>5.117556080000002</v>
       </c>
       <c r="Q41">
-        <v>12.088635554</v>
+        <v>11.93755608</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1235777316649599</v>
+        <v>0.1248002717522766</v>
       </c>
       <c r="T41">
-        <v>1.131760765008883</v>
+        <v>1.149550212899132</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.09</v>
       </c>
       <c r="W41">
-        <v>0.055783</v>
+        <v>0.05833100000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.527936585863821</v>
+        <v>3.289484397747519</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09821256305136594</v>
+        <v>0.09829361978710638</v>
       </c>
       <c r="C42">
-        <v>65.33559385839285</v>
+        <v>64.22775872565299</v>
       </c>
       <c r="D42">
-        <v>97.03559385839284</v>
+        <v>96.88575872565299</v>
       </c>
       <c r="E42">
-        <v>-15.18</v>
+        <v>-14.22199999999999</v>
       </c>
       <c r="F42">
-        <v>38.31999999999999</v>
+        <v>39.278</v>
       </c>
       <c r="G42">
         <v>6.62</v>
@@ -4719,28 +4719,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M42">
-        <v>2.456312</v>
+        <v>2.5177198</v>
       </c>
       <c r="N42">
-        <v>5.623688000000002</v>
+        <v>5.562280200000002</v>
       </c>
       <c r="O42">
-        <v>0.5061319200000002</v>
+        <v>0.5006052180000001</v>
       </c>
       <c r="P42">
-        <v>5.117556080000002</v>
+        <v>5.061674982000001</v>
       </c>
       <c r="Q42">
-        <v>11.93755608</v>
+        <v>11.881674982</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1248002717522766</v>
+        <v>0.1260642538764515</v>
       </c>
       <c r="T42">
-        <v>1.149550212899132</v>
+        <v>1.167942692921254</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.289484397747519</v>
+        <v>3.209253070973189</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09829361978710638</v>
+        <v>0.09837467652284679</v>
       </c>
       <c r="C43">
-        <v>64.22775872565299</v>
+        <v>63.12038560799585</v>
       </c>
       <c r="D43">
-        <v>96.88575872565299</v>
+        <v>96.73638560799584</v>
       </c>
       <c r="E43">
-        <v>-14.22199999999999</v>
+        <v>-13.264</v>
       </c>
       <c r="F43">
-        <v>39.278</v>
+        <v>40.236</v>
       </c>
       <c r="G43">
         <v>6.62</v>
@@ -4801,28 +4801,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M43">
-        <v>2.5177198</v>
+        <v>2.5791276</v>
       </c>
       <c r="N43">
-        <v>5.562280200000002</v>
+        <v>5.500872400000002</v>
       </c>
       <c r="O43">
-        <v>0.5006052180000001</v>
+        <v>0.4950785160000002</v>
       </c>
       <c r="P43">
-        <v>5.061674982000001</v>
+        <v>5.005793884000002</v>
       </c>
       <c r="Q43">
-        <v>11.881674982</v>
+        <v>11.825793884</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1260642538764515</v>
+        <v>0.1273718215911152</v>
       </c>
       <c r="T43">
-        <v>1.167942692921254</v>
+        <v>1.186969396392414</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.209253070973189</v>
+        <v>3.132842283569065</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09837467652284679</v>
+        <v>0.09845573325858721</v>
       </c>
       <c r="C44">
-        <v>63.12038560799586</v>
+        <v>62.01347237178272</v>
       </c>
       <c r="D44">
-        <v>96.73638560799584</v>
+        <v>96.58747237178271</v>
       </c>
       <c r="E44">
-        <v>-13.264</v>
+        <v>-12.306</v>
       </c>
       <c r="F44">
-        <v>40.23599999999999</v>
+        <v>41.194</v>
       </c>
       <c r="G44">
         <v>6.62</v>
@@ -4883,28 +4883,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M44">
-        <v>2.5791276</v>
+        <v>2.6405354</v>
       </c>
       <c r="N44">
-        <v>5.500872400000002</v>
+        <v>5.439464600000002</v>
       </c>
       <c r="O44">
-        <v>0.4950785160000002</v>
+        <v>0.4895518140000001</v>
       </c>
       <c r="P44">
-        <v>5.005793884000002</v>
+        <v>4.949912786000001</v>
       </c>
       <c r="Q44">
-        <v>11.825793884</v>
+        <v>11.769912786</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1273718215911152</v>
+        <v>0.1287252688747144</v>
       </c>
       <c r="T44">
-        <v>1.186969396392414</v>
+        <v>1.206663703494142</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.132842283569065</v>
+        <v>3.059985486276761</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09845573325858721</v>
+        <v>0.1016599099943276</v>
       </c>
       <c r="C45">
-        <v>62.01347237178272</v>
+        <v>55.51512452716458</v>
       </c>
       <c r="D45">
-        <v>96.58747237178271</v>
+        <v>91.04712452716457</v>
       </c>
       <c r="E45">
-        <v>-12.306</v>
+        <v>-11.348</v>
       </c>
       <c r="F45">
-        <v>41.194</v>
+        <v>42.15199999999999</v>
       </c>
       <c r="G45">
         <v>6.62</v>
@@ -4965,45 +4965,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M45">
-        <v>2.6405354</v>
+        <v>3.0307288</v>
       </c>
       <c r="N45">
-        <v>5.439464600000002</v>
+        <v>5.049271200000002</v>
       </c>
       <c r="O45">
-        <v>0.4895518140000001</v>
+        <v>0.4544344080000001</v>
       </c>
       <c r="P45">
-        <v>4.949912786000001</v>
+        <v>4.594836792000002</v>
       </c>
       <c r="Q45">
-        <v>11.769912786</v>
+        <v>11.414836792</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1287252688747144</v>
+        <v>0.1301270535612993</v>
       </c>
       <c r="T45">
-        <v>1.206663703494142</v>
+        <v>1.227061378706646</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.09</v>
       </c>
       <c r="W45">
-        <v>0.05833100000000001</v>
+        <v>0.065429</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.059985486276761</v>
+        <v>2.666025412765405</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1016599099943276</v>
+        <v>0.1018119467300681</v>
       </c>
       <c r="C46">
-        <v>55.51512452716458</v>
+        <v>54.3099896136367</v>
       </c>
       <c r="D46">
-        <v>91.04712452716457</v>
+        <v>90.79998961363668</v>
       </c>
       <c r="E46">
-        <v>-11.348</v>
+        <v>-10.39</v>
       </c>
       <c r="F46">
-        <v>42.15199999999999</v>
+        <v>43.10999999999999</v>
       </c>
       <c r="G46">
         <v>6.62</v>
@@ -5047,28 +5047,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M46">
-        <v>3.0307288</v>
+        <v>3.099609</v>
       </c>
       <c r="N46">
-        <v>5.049271200000002</v>
+        <v>4.980391000000003</v>
       </c>
       <c r="O46">
-        <v>0.4544344080000001</v>
+        <v>0.4482351900000002</v>
       </c>
       <c r="P46">
-        <v>4.594836792000002</v>
+        <v>4.532155810000003</v>
       </c>
       <c r="Q46">
-        <v>11.414836792</v>
+        <v>11.35215581</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1301270535612993</v>
+        <v>0.1315798122364874</v>
       </c>
       <c r="T46">
-        <v>1.227061378706646</v>
+        <v>1.248200787563241</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.666025412765405</v>
+        <v>2.606780403592841</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1018119467300681</v>
+        <v>0.1019639834658085</v>
       </c>
       <c r="C47">
-        <v>54.3099896136367</v>
+        <v>53.10619269585707</v>
       </c>
       <c r="D47">
-        <v>90.79998961363668</v>
+        <v>90.55419269585705</v>
       </c>
       <c r="E47">
-        <v>-10.39</v>
+        <v>-9.432000000000002</v>
       </c>
       <c r="F47">
-        <v>43.10999999999999</v>
+        <v>44.06799999999999</v>
       </c>
       <c r="G47">
         <v>6.62</v>
@@ -5129,28 +5129,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M47">
-        <v>3.099609</v>
+        <v>3.1684892</v>
       </c>
       <c r="N47">
-        <v>4.980391000000003</v>
+        <v>4.911510800000002</v>
       </c>
       <c r="O47">
-        <v>0.4482351900000002</v>
+        <v>0.4420359720000002</v>
       </c>
       <c r="P47">
-        <v>4.532155810000003</v>
+        <v>4.469474828000002</v>
       </c>
       <c r="Q47">
-        <v>11.35215581</v>
+        <v>11.289474828</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1315798122364874</v>
+        <v>0.1330863767885342</v>
       </c>
       <c r="T47">
-        <v>1.248200787563241</v>
+        <v>1.270123137488598</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.606780403592841</v>
+        <v>2.550111264384301</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1019639834658085</v>
+        <v>0.1037840502015489</v>
       </c>
       <c r="C48">
-        <v>53.10619269585707</v>
+        <v>49.30577873314364</v>
       </c>
       <c r="D48">
-        <v>90.55419269585705</v>
+        <v>87.71177873314363</v>
       </c>
       <c r="E48">
-        <v>-9.432000000000002</v>
+        <v>-8.473999999999997</v>
       </c>
       <c r="F48">
-        <v>44.06799999999999</v>
+        <v>45.026</v>
       </c>
       <c r="G48">
         <v>6.62</v>
@@ -5211,45 +5211,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M48">
-        <v>3.1684892</v>
+        <v>3.4129708</v>
       </c>
       <c r="N48">
-        <v>4.911510800000002</v>
+        <v>4.667029200000002</v>
       </c>
       <c r="O48">
-        <v>0.4420359720000002</v>
+        <v>0.4200326280000001</v>
       </c>
       <c r="P48">
-        <v>4.469474828000002</v>
+        <v>4.246996572000001</v>
       </c>
       <c r="Q48">
-        <v>11.289474828</v>
+        <v>11.066996572</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1330863767885342</v>
+        <v>0.1346497928331112</v>
       </c>
       <c r="T48">
-        <v>1.270123137488598</v>
+        <v>1.292872745901705</v>
       </c>
       <c r="U48">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.09</v>
       </c>
       <c r="W48">
-        <v>0.065429</v>
+        <v>0.06897800000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.550111264384301</v>
+        <v>2.367438947910132</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1037840502015489</v>
+        <v>0.1039715769372894</v>
       </c>
       <c r="C49">
-        <v>49.30577873314364</v>
+        <v>48.06502374492068</v>
       </c>
       <c r="D49">
-        <v>87.71177873314363</v>
+        <v>87.42902374492067</v>
       </c>
       <c r="E49">
-        <v>-8.473999999999997</v>
+        <v>-7.515999999999998</v>
       </c>
       <c r="F49">
-        <v>45.026</v>
+        <v>45.98399999999999</v>
       </c>
       <c r="G49">
         <v>6.62</v>
@@ -5293,28 +5293,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M49">
-        <v>3.4129708</v>
+        <v>3.4855872</v>
       </c>
       <c r="N49">
-        <v>4.667029200000002</v>
+        <v>4.594412800000002</v>
       </c>
       <c r="O49">
-        <v>0.4200326280000001</v>
+        <v>0.4134971520000002</v>
       </c>
       <c r="P49">
-        <v>4.246996572000001</v>
+        <v>4.180915648000002</v>
       </c>
       <c r="Q49">
-        <v>11.066996572</v>
+        <v>11.000915648</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1346497928331112</v>
+        <v>0.136273340264018</v>
       </c>
       <c r="T49">
-        <v>1.292872745901705</v>
+        <v>1.316497339253778</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.367438947910132</v>
+        <v>2.318117303162005</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1039715769372894</v>
+        <v>0.1041591036730298</v>
       </c>
       <c r="C50">
-        <v>48.06502374492072</v>
+        <v>46.82608592374177</v>
       </c>
       <c r="D50">
-        <v>87.4290237449207</v>
+        <v>87.14808592374176</v>
       </c>
       <c r="E50">
-        <v>-7.516000000000005</v>
+        <v>-6.558</v>
       </c>
       <c r="F50">
-        <v>45.98399999999999</v>
+        <v>46.94199999999999</v>
       </c>
       <c r="G50">
         <v>6.62</v>
@@ -5375,28 +5375,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M50">
-        <v>3.485587199999999</v>
+        <v>3.5582036</v>
       </c>
       <c r="N50">
-        <v>4.594412800000002</v>
+        <v>4.521796400000002</v>
       </c>
       <c r="O50">
-        <v>0.4134971520000002</v>
+        <v>0.4069616760000002</v>
       </c>
       <c r="P50">
-        <v>4.180915648000002</v>
+        <v>4.114834724000002</v>
       </c>
       <c r="Q50">
-        <v>11.000915648</v>
+        <v>10.934834724</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.136273340264018</v>
+        <v>0.137960556221627</v>
       </c>
       <c r="T50">
-        <v>1.316497339253778</v>
+        <v>1.341048387247108</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.318117303162005</v>
+        <v>2.270808786770943</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1041591036730298</v>
+        <v>0.1043466304087702</v>
       </c>
       <c r="C51">
-        <v>46.82608592374177</v>
+        <v>45.58894780827377</v>
       </c>
       <c r="D51">
-        <v>87.14808592374176</v>
+        <v>86.86894780827376</v>
       </c>
       <c r="E51">
-        <v>-6.558</v>
+        <v>-5.600000000000001</v>
       </c>
       <c r="F51">
-        <v>46.94199999999999</v>
+        <v>47.89999999999999</v>
       </c>
       <c r="G51">
         <v>6.62</v>
@@ -5457,28 +5457,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M51">
-        <v>3.5582036</v>
+        <v>3.630819999999999</v>
       </c>
       <c r="N51">
-        <v>4.521796400000002</v>
+        <v>4.449180000000002</v>
       </c>
       <c r="O51">
-        <v>0.4069616760000002</v>
+        <v>0.4004262000000002</v>
       </c>
       <c r="P51">
-        <v>4.114834724000002</v>
+        <v>4.048753800000002</v>
       </c>
       <c r="Q51">
-        <v>10.934834724</v>
+        <v>10.8687538</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.137960556221627</v>
+        <v>0.1397152608175404</v>
       </c>
       <c r="T51">
-        <v>1.341048387247108</v>
+        <v>1.366581477160171</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.270808786770943</v>
+        <v>2.225392611035525</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1043466304087702</v>
+        <v>0.1045341571445106</v>
       </c>
       <c r="C52">
-        <v>45.58894780827377</v>
+        <v>44.35359216018625</v>
       </c>
       <c r="D52">
-        <v>86.86894780827376</v>
+        <v>86.59159216018624</v>
       </c>
       <c r="E52">
-        <v>-5.600000000000001</v>
+        <v>-4.642000000000003</v>
       </c>
       <c r="F52">
-        <v>47.89999999999999</v>
+        <v>48.85799999999999</v>
       </c>
       <c r="G52">
         <v>6.62</v>
@@ -5539,28 +5539,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M52">
-        <v>3.630819999999999</v>
+        <v>3.7034364</v>
       </c>
       <c r="N52">
-        <v>4.449180000000002</v>
+        <v>4.376563600000003</v>
       </c>
       <c r="O52">
-        <v>0.4004262000000002</v>
+        <v>0.3938907240000002</v>
       </c>
       <c r="P52">
-        <v>4.048753800000002</v>
+        <v>3.982672876000002</v>
       </c>
       <c r="Q52">
-        <v>10.8687538</v>
+        <v>10.802672876</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1397152608175404</v>
+        <v>0.1415415860092053</v>
       </c>
       <c r="T52">
-        <v>1.366581477160171</v>
+        <v>1.393156734008462</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.225392611035525</v>
+        <v>2.181757461799534</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1045341571445106</v>
+        <v>0.104721683880251</v>
       </c>
       <c r="C53">
-        <v>44.35359216018625</v>
+        <v>43.12000196060254</v>
       </c>
       <c r="D53">
-        <v>86.59159216018624</v>
+        <v>86.31600196060253</v>
       </c>
       <c r="E53">
-        <v>-4.642000000000003</v>
+        <v>-3.683999999999997</v>
       </c>
       <c r="F53">
-        <v>48.85799999999999</v>
+        <v>49.816</v>
       </c>
       <c r="G53">
         <v>6.62</v>
@@ -5621,28 +5621,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M53">
-        <v>3.7034364</v>
+        <v>3.7760528</v>
       </c>
       <c r="N53">
-        <v>4.376563600000003</v>
+        <v>4.303947200000001</v>
       </c>
       <c r="O53">
-        <v>0.3938907240000002</v>
+        <v>0.3873552480000001</v>
       </c>
       <c r="P53">
-        <v>3.982672876000002</v>
+        <v>3.916591952000001</v>
       </c>
       <c r="Q53">
-        <v>10.802672876</v>
+        <v>10.736591952</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1415415860092053</v>
+        <v>0.1434440080838564</v>
       </c>
       <c r="T53">
-        <v>1.393156734008462</v>
+        <v>1.420839293225431</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.181757461799534</v>
+        <v>2.139800587534157</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.104721683880251</v>
+        <v>0.1049092106159915</v>
       </c>
       <c r="C54">
-        <v>43.12000196060254</v>
+        <v>41.88816040661877</v>
       </c>
       <c r="D54">
-        <v>86.31600196060253</v>
+        <v>86.04216040661876</v>
       </c>
       <c r="E54">
-        <v>-3.683999999999997</v>
+        <v>-2.725999999999999</v>
       </c>
       <c r="F54">
-        <v>49.816</v>
+        <v>50.77399999999999</v>
       </c>
       <c r="G54">
         <v>6.62</v>
@@ -5703,28 +5703,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M54">
-        <v>3.7760528</v>
+        <v>3.8486692</v>
       </c>
       <c r="N54">
-        <v>4.303947200000001</v>
+        <v>4.231330800000002</v>
       </c>
       <c r="O54">
-        <v>0.3873552480000001</v>
+        <v>0.3808197720000002</v>
       </c>
       <c r="P54">
-        <v>3.916591952000001</v>
+        <v>3.850511028000002</v>
       </c>
       <c r="Q54">
-        <v>10.736591952</v>
+        <v>10.670511028</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1434440080838564</v>
+        <v>0.1454273842893436</v>
       </c>
       <c r="T54">
-        <v>1.420839293225431</v>
+        <v>1.449699833685676</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.139800587534157</v>
+        <v>2.099426991542948</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1049092106159915</v>
+        <v>0.1050967373517319</v>
       </c>
       <c r="C55">
-        <v>41.88816040661877</v>
+        <v>40.65805090788873</v>
       </c>
       <c r="D55">
-        <v>86.04216040661876</v>
+        <v>85.77005090788872</v>
       </c>
       <c r="E55">
-        <v>-2.725999999999999</v>
+        <v>-1.768000000000001</v>
       </c>
       <c r="F55">
-        <v>50.77399999999999</v>
+        <v>51.73199999999999</v>
       </c>
       <c r="G55">
         <v>6.62</v>
@@ -5785,28 +5785,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M55">
-        <v>3.8486692</v>
+        <v>3.9212856</v>
       </c>
       <c r="N55">
-        <v>4.231330800000002</v>
+        <v>4.158714400000003</v>
       </c>
       <c r="O55">
-        <v>0.3808197720000002</v>
+        <v>0.3742842960000002</v>
       </c>
       <c r="P55">
-        <v>3.850511028000002</v>
+        <v>3.784430104000002</v>
       </c>
       <c r="Q55">
-        <v>10.670511028</v>
+        <v>10.604430104</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1454273842893436</v>
+        <v>0.1474969942428954</v>
       </c>
       <c r="T55">
-        <v>1.449699833685676</v>
+        <v>1.479815180252888</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.099426991542948</v>
+        <v>2.060548713921782</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1050967373517319</v>
+        <v>0.1052842640874723</v>
       </c>
       <c r="C56">
-        <v>40.65805090788873</v>
+        <v>39.42965708327328</v>
       </c>
       <c r="D56">
-        <v>85.77005090788872</v>
+        <v>85.49965708327328</v>
       </c>
       <c r="E56">
-        <v>-1.768000000000001</v>
+        <v>-0.8099999999999952</v>
       </c>
       <c r="F56">
-        <v>51.73199999999999</v>
+        <v>52.69</v>
       </c>
       <c r="G56">
         <v>6.62</v>
@@ -5867,28 +5867,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M56">
-        <v>3.9212856</v>
+        <v>3.993902</v>
       </c>
       <c r="N56">
-        <v>4.158714400000003</v>
+        <v>4.086098000000002</v>
       </c>
       <c r="O56">
-        <v>0.3742842960000002</v>
+        <v>0.3677488200000001</v>
       </c>
       <c r="P56">
-        <v>3.784430104000002</v>
+        <v>3.718349180000001</v>
       </c>
       <c r="Q56">
-        <v>10.604430104</v>
+        <v>10.53834918</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1474969942428954</v>
+        <v>0.1496585868610496</v>
       </c>
       <c r="T56">
-        <v>1.479815180252888</v>
+        <v>1.511268986667531</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.060548713921782</v>
+        <v>2.023084191850476</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1052842640874723</v>
+        <v>0.1127081108232127</v>
       </c>
       <c r="C57">
-        <v>39.42965708327328</v>
+        <v>28.9849694106575</v>
       </c>
       <c r="D57">
-        <v>85.49965708327328</v>
+        <v>76.01296941065749</v>
       </c>
       <c r="E57">
-        <v>-0.8099999999999952</v>
+        <v>0.1480000000000032</v>
       </c>
       <c r="F57">
-        <v>52.69</v>
+        <v>53.648</v>
       </c>
       <c r="G57">
         <v>6.62</v>
@@ -5949,45 +5949,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M57">
-        <v>3.993902</v>
+        <v>4.82832</v>
       </c>
       <c r="N57">
-        <v>4.086098000000002</v>
+        <v>3.251680000000002</v>
       </c>
       <c r="O57">
-        <v>0.3677488200000001</v>
+        <v>0.2926512000000002</v>
       </c>
       <c r="P57">
-        <v>3.718349180000001</v>
+        <v>2.959028800000002</v>
       </c>
       <c r="Q57">
-        <v>10.53834918</v>
+        <v>9.779028800000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1496585868610496</v>
+        <v>0.1519184336891199</v>
       </c>
       <c r="T57">
-        <v>1.511268986667531</v>
+        <v>1.544152511555567</v>
       </c>
       <c r="U57">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V57">
         <v>0.09</v>
       </c>
       <c r="W57">
-        <v>0.06897800000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.023084191850476</v>
+        <v>1.673459919806476</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1127081108232127</v>
+        <v>0.1130248575589532</v>
       </c>
       <c r="C58">
-        <v>28.9849694106575</v>
+        <v>27.66881528718245</v>
       </c>
       <c r="D58">
-        <v>76.01296941065749</v>
+        <v>75.65481528718244</v>
       </c>
       <c r="E58">
-        <v>0.1480000000000032</v>
+        <v>1.106000000000002</v>
       </c>
       <c r="F58">
-        <v>53.648</v>
+        <v>54.60599999999999</v>
       </c>
       <c r="G58">
         <v>6.62</v>
@@ -6031,28 +6031,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M58">
-        <v>4.82832</v>
+        <v>4.91454</v>
       </c>
       <c r="N58">
-        <v>3.251680000000002</v>
+        <v>3.165460000000002</v>
       </c>
       <c r="O58">
-        <v>0.2926512000000002</v>
+        <v>0.2848914000000002</v>
       </c>
       <c r="P58">
-        <v>2.959028800000002</v>
+        <v>2.880568600000002</v>
       </c>
       <c r="Q58">
-        <v>9.779028800000001</v>
+        <v>9.7005686</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1519184336891199</v>
+        <v>0.1542833896719841</v>
       </c>
       <c r="T58">
-        <v>1.544152511555567</v>
+        <v>1.578565502717466</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.673459919806476</v>
+        <v>1.644100973844958</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1130248575589532</v>
+        <v>0.1133416042946936</v>
       </c>
       <c r="C59">
-        <v>27.66881528718245</v>
+        <v>26.35602040134136</v>
       </c>
       <c r="D59">
-        <v>75.65481528718244</v>
+        <v>75.30002040134136</v>
       </c>
       <c r="E59">
-        <v>1.106000000000002</v>
+        <v>2.064000000000007</v>
       </c>
       <c r="F59">
-        <v>54.60599999999999</v>
+        <v>55.564</v>
       </c>
       <c r="G59">
         <v>6.62</v>
@@ -6113,28 +6113,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M59">
-        <v>4.91454</v>
+        <v>5.00076</v>
       </c>
       <c r="N59">
-        <v>3.165460000000002</v>
+        <v>3.079240000000002</v>
       </c>
       <c r="O59">
-        <v>0.2848914000000002</v>
+        <v>0.2771316000000002</v>
       </c>
       <c r="P59">
-        <v>2.880568600000002</v>
+        <v>2.802108400000002</v>
       </c>
       <c r="Q59">
-        <v>9.7005686</v>
+        <v>9.622108400000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1542833896719841</v>
+        <v>0.1567609626064133</v>
       </c>
       <c r="T59">
-        <v>1.578565502717466</v>
+        <v>1.614617207744216</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.644100973844958</v>
+        <v>1.61575440533039</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1133416042946936</v>
+        <v>0.113658351030434</v>
       </c>
       <c r="C60">
-        <v>26.35602040134135</v>
+        <v>25.04653771275354</v>
       </c>
       <c r="D60">
-        <v>75.30002040134133</v>
+        <v>74.94853771275352</v>
       </c>
       <c r="E60">
-        <v>2.063999999999993</v>
+        <v>3.021999999999991</v>
       </c>
       <c r="F60">
-        <v>55.56399999999999</v>
+        <v>56.52199999999998</v>
       </c>
       <c r="G60">
         <v>6.62</v>
@@ -6195,28 +6195,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M60">
-        <v>5.000759999999999</v>
+        <v>5.086979999999999</v>
       </c>
       <c r="N60">
-        <v>3.079240000000003</v>
+        <v>2.993020000000003</v>
       </c>
       <c r="O60">
-        <v>0.2771316000000003</v>
+        <v>0.2693718000000003</v>
       </c>
       <c r="P60">
-        <v>2.802108400000003</v>
+        <v>2.723648200000003</v>
       </c>
       <c r="Q60">
-        <v>9.622108400000002</v>
+        <v>9.543648200000003</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1567609626064133</v>
+        <v>0.1593593927571562</v>
       </c>
       <c r="T60">
-        <v>1.614617207744216</v>
+        <v>1.652427532528369</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.61575440533039</v>
+        <v>1.588368737443435</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.113658351030434</v>
+        <v>0.1139750977661745</v>
       </c>
       <c r="C61">
-        <v>25.04653771275354</v>
+        <v>23.7403210552512</v>
       </c>
       <c r="D61">
-        <v>74.94853771275352</v>
+        <v>74.60032105525119</v>
       </c>
       <c r="E61">
-        <v>3.021999999999991</v>
+        <v>3.979999999999997</v>
       </c>
       <c r="F61">
-        <v>56.52199999999998</v>
+        <v>57.47999999999999</v>
       </c>
       <c r="G61">
         <v>6.62</v>
@@ -6277,28 +6277,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M61">
-        <v>5.086979999999999</v>
+        <v>5.173199999999999</v>
       </c>
       <c r="N61">
-        <v>2.993020000000003</v>
+        <v>2.906800000000003</v>
       </c>
       <c r="O61">
-        <v>0.2693718000000003</v>
+        <v>0.2616120000000003</v>
       </c>
       <c r="P61">
-        <v>2.723648200000003</v>
+        <v>2.645188000000003</v>
       </c>
       <c r="Q61">
-        <v>9.543648200000003</v>
+        <v>9.465188000000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1593593927571562</v>
+        <v>0.1620877444154361</v>
       </c>
       <c r="T61">
-        <v>1.652427532528369</v>
+        <v>1.69212837355173</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.588368737443435</v>
+        <v>1.561895925152711</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1139750977661745</v>
+        <v>0.1142918445019149</v>
       </c>
       <c r="C62">
-        <v>23.7403210552512</v>
+        <v>22.43732511666499</v>
       </c>
       <c r="D62">
-        <v>74.60032105525119</v>
+        <v>74.25532511666498</v>
       </c>
       <c r="E62">
-        <v>3.979999999999997</v>
+        <v>4.937999999999995</v>
       </c>
       <c r="F62">
-        <v>57.47999999999999</v>
+        <v>58.43799999999999</v>
       </c>
       <c r="G62">
         <v>6.62</v>
@@ -6359,28 +6359,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M62">
-        <v>5.173199999999999</v>
+        <v>5.259419999999999</v>
       </c>
       <c r="N62">
-        <v>2.906800000000003</v>
+        <v>2.820580000000003</v>
       </c>
       <c r="O62">
-        <v>0.2616120000000003</v>
+        <v>0.2538522000000003</v>
       </c>
       <c r="P62">
-        <v>2.645188000000003</v>
+        <v>2.566727800000003</v>
       </c>
       <c r="Q62">
-        <v>9.465188000000001</v>
+        <v>9.386727800000003</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1620877444154361</v>
+        <v>0.1649560115433715</v>
       </c>
       <c r="T62">
-        <v>1.69212837355173</v>
+        <v>1.733865155140392</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.561895925152711</v>
+        <v>1.536291073920699</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1142918445019149</v>
+        <v>0.1146085912376553</v>
       </c>
       <c r="C63">
-        <v>22.43732511666499</v>
+        <v>21.13750541916802</v>
       </c>
       <c r="D63">
-        <v>74.25532511666498</v>
+        <v>73.913505419168</v>
       </c>
       <c r="E63">
-        <v>4.937999999999995</v>
+        <v>5.895999999999994</v>
       </c>
       <c r="F63">
-        <v>58.43799999999999</v>
+        <v>59.39599999999999</v>
       </c>
       <c r="G63">
         <v>6.62</v>
@@ -6441,28 +6441,28 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M63">
-        <v>5.259419999999999</v>
+        <v>5.345639999999999</v>
       </c>
       <c r="N63">
-        <v>2.820580000000003</v>
+        <v>2.734360000000003</v>
       </c>
       <c r="O63">
-        <v>0.2538522000000003</v>
+        <v>0.2460924000000003</v>
       </c>
       <c r="P63">
-        <v>2.566727800000003</v>
+        <v>2.488267600000003</v>
       </c>
       <c r="Q63">
-        <v>9.386727800000003</v>
+        <v>9.308267600000002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1649560115433715</v>
+        <v>0.1679752400990929</v>
       </c>
       <c r="T63">
-        <v>1.733865155140392</v>
+        <v>1.777798609444246</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.536291073920699</v>
+        <v>1.511512185631656</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1146085912376553</v>
+        <v>0.1484669551553612</v>
       </c>
       <c r="C64">
-        <v>21.13750541916802</v>
+        <v>-4.196306263651067</v>
       </c>
       <c r="D64">
-        <v>73.913505419168</v>
+        <v>49.53769373634893</v>
       </c>
       <c r="E64">
-        <v>5.895999999999994</v>
+        <v>6.853999999999999</v>
       </c>
       <c r="F64">
-        <v>59.39599999999999</v>
+        <v>60.35399999999999</v>
       </c>
       <c r="G64">
         <v>6.62</v>
@@ -6523,45 +6523,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M64">
-        <v>5.345639999999999</v>
+        <v>8.8599672</v>
       </c>
       <c r="N64">
-        <v>2.734360000000003</v>
+        <v>-0.779967199999998</v>
       </c>
       <c r="O64">
-        <v>0.2460924000000003</v>
+        <v>-0.07019704799999982</v>
       </c>
       <c r="P64">
-        <v>2.488267600000003</v>
+        <v>-0.7097701519999982</v>
       </c>
       <c r="Q64">
-        <v>9.308267600000002</v>
+        <v>6.110229848000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1679752400990929</v>
+        <v>0.1718209982475766</v>
       </c>
       <c r="T64">
-        <v>1.777798609444246</v>
+        <v>1.83375907641847</v>
       </c>
       <c r="U64">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.09</v>
+        <v>0.08207705328751107</v>
       </c>
       <c r="W64">
-        <v>0.0819</v>
+        <v>0.1347510885773934</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.511512185631656</v>
+        <v>0.9119672587501229</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1484669551553612</v>
+        <v>0.1494769551553612</v>
       </c>
       <c r="C65">
-        <v>-4.196306263651067</v>
+        <v>-5.636892491214731</v>
       </c>
       <c r="D65">
-        <v>49.53769373634893</v>
+        <v>49.05510750878526</v>
       </c>
       <c r="E65">
-        <v>6.853999999999999</v>
+        <v>7.811999999999998</v>
       </c>
       <c r="F65">
-        <v>60.35399999999999</v>
+        <v>61.31199999999999</v>
       </c>
       <c r="G65">
         <v>6.62</v>
@@ -6605,37 +6605,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M65">
-        <v>8.8599672</v>
+        <v>9.0006016</v>
       </c>
       <c r="N65">
-        <v>-0.779967199999998</v>
+        <v>-0.9206015999999977</v>
       </c>
       <c r="O65">
-        <v>-0.07019704799999982</v>
+        <v>-0.08285414399999978</v>
       </c>
       <c r="P65">
-        <v>-0.7097701519999982</v>
+        <v>-0.8377474559999979</v>
       </c>
       <c r="Q65">
-        <v>6.110229848000001</v>
+        <v>5.982252544000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1718209982475766</v>
+        <v>0.1753215815322315</v>
       </c>
       <c r="T65">
-        <v>1.83375907641847</v>
+        <v>1.884696828541205</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.08207705328751107</v>
+        <v>0.0807945993298937</v>
       </c>
       <c r="W65">
-        <v>0.1347510885773934</v>
+        <v>0.1349393528183716</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9119672587501229</v>
+        <v>0.8977177703321523</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1494769551553612</v>
+        <v>0.1504869551553612</v>
       </c>
       <c r="C66">
-        <v>-5.636892491214731</v>
+        <v>-7.068166916957125</v>
       </c>
       <c r="D66">
-        <v>49.05510750878526</v>
+        <v>48.58183308304287</v>
       </c>
       <c r="E66">
-        <v>7.811999999999998</v>
+        <v>8.769999999999996</v>
       </c>
       <c r="F66">
-        <v>61.31199999999999</v>
+        <v>62.26999999999999</v>
       </c>
       <c r="G66">
         <v>6.62</v>
@@ -6687,37 +6687,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M66">
-        <v>9.0006016</v>
+        <v>9.141235999999999</v>
       </c>
       <c r="N66">
-        <v>-0.9206015999999977</v>
+        <v>-1.061235999999997</v>
       </c>
       <c r="O66">
-        <v>-0.08285414399999978</v>
+        <v>-0.09551123999999976</v>
       </c>
       <c r="P66">
-        <v>-0.8377474559999979</v>
+        <v>-0.9657247599999976</v>
       </c>
       <c r="Q66">
-        <v>5.982252544000001</v>
+        <v>5.854275240000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1753215815322315</v>
+        <v>0.1790221981474381</v>
       </c>
       <c r="T66">
-        <v>1.884696828541205</v>
+        <v>1.938545309356668</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.0807945993298937</v>
+        <v>0.07955160549404919</v>
       </c>
       <c r="W66">
-        <v>0.1349393528183716</v>
+        <v>0.1351218243134736</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8977177703321523</v>
+        <v>0.8839067277116577</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1504869551553612</v>
+        <v>0.1514969551553612</v>
       </c>
       <c r="C67">
-        <v>-7.068166916957125</v>
+        <v>-8.490396481013626</v>
       </c>
       <c r="D67">
-        <v>48.58183308304287</v>
+        <v>48.11760351898637</v>
       </c>
       <c r="E67">
-        <v>8.769999999999996</v>
+        <v>9.728000000000002</v>
       </c>
       <c r="F67">
-        <v>62.26999999999999</v>
+        <v>63.22799999999999</v>
       </c>
       <c r="G67">
         <v>6.62</v>
@@ -6769,37 +6769,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M67">
-        <v>9.141235999999999</v>
+        <v>9.281870400000001</v>
       </c>
       <c r="N67">
-        <v>-1.061235999999997</v>
+        <v>-1.201870399999999</v>
       </c>
       <c r="O67">
-        <v>-0.09551123999999976</v>
+        <v>-0.1081683359999999</v>
       </c>
       <c r="P67">
-        <v>-0.9657247599999976</v>
+        <v>-1.093702063999999</v>
       </c>
       <c r="Q67">
-        <v>5.854275240000002</v>
+        <v>5.726297936</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1790221981474381</v>
+        <v>0.182940498092951</v>
       </c>
       <c r="T67">
-        <v>1.938545309356668</v>
+        <v>1.995561347867158</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.07955160549404919</v>
+        <v>0.07834627813807872</v>
       </c>
       <c r="W67">
-        <v>0.1351218243134736</v>
+        <v>0.1352987663693301</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8839067277116577</v>
+        <v>0.8705142015342081</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1514969551553612</v>
+        <v>0.1525069551553612</v>
       </c>
       <c r="C68">
-        <v>-8.490396481013626</v>
+        <v>-9.903838016979272</v>
       </c>
       <c r="D68">
-        <v>48.11760351898637</v>
+        <v>47.66216198302072</v>
       </c>
       <c r="E68">
-        <v>9.728000000000002</v>
+        <v>10.686</v>
       </c>
       <c r="F68">
-        <v>63.22799999999999</v>
+        <v>64.18599999999999</v>
       </c>
       <c r="G68">
         <v>6.62</v>
@@ -6851,37 +6851,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M68">
-        <v>9.281870400000001</v>
+        <v>9.4225048</v>
       </c>
       <c r="N68">
-        <v>-1.201870399999999</v>
+        <v>-1.342504799999999</v>
       </c>
       <c r="O68">
-        <v>-0.1081683359999999</v>
+        <v>-0.1208254319999999</v>
       </c>
       <c r="P68">
-        <v>-1.093702063999999</v>
+        <v>-1.221679367999999</v>
       </c>
       <c r="Q68">
-        <v>5.726297936</v>
+        <v>5.598320632000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.182940498092951</v>
+        <v>0.1870962707624344</v>
       </c>
       <c r="T68">
-        <v>1.995561347867158</v>
+        <v>2.056032903863133</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.07834627813807872</v>
+        <v>0.07717693070318205</v>
       </c>
       <c r="W68">
-        <v>0.1352987663693301</v>
+        <v>0.1354704265727729</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8705142015342081</v>
+        <v>0.8575214522575783</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1525069551553612</v>
+        <v>0.1535169551553612</v>
       </c>
       <c r="C69">
-        <v>-9.903838016979272</v>
+        <v>-11.30873872572491</v>
       </c>
       <c r="D69">
-        <v>47.66216198302072</v>
+        <v>47.21526127427509</v>
       </c>
       <c r="E69">
-        <v>10.686</v>
+        <v>11.644</v>
       </c>
       <c r="F69">
-        <v>64.18599999999999</v>
+        <v>65.14399999999999</v>
       </c>
       <c r="G69">
         <v>6.62</v>
@@ -6933,37 +6933,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M69">
-        <v>9.4225048</v>
+        <v>9.5631392</v>
       </c>
       <c r="N69">
-        <v>-1.342504799999999</v>
+        <v>-1.483139199999998</v>
       </c>
       <c r="O69">
-        <v>-0.1208254319999999</v>
+        <v>-0.1334825279999999</v>
       </c>
       <c r="P69">
-        <v>-1.221679367999999</v>
+        <v>-1.349656671999999</v>
       </c>
       <c r="Q69">
-        <v>5.598320632000001</v>
+        <v>5.470343328000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1870962707624344</v>
+        <v>0.1915117792237605</v>
       </c>
       <c r="T69">
-        <v>2.056032903863133</v>
+        <v>2.120283932108856</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.07717693070318205</v>
+        <v>0.07604197583989995</v>
       </c>
       <c r="W69">
-        <v>0.1354704265727729</v>
+        <v>0.1356370379467027</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8575214522575783</v>
+        <v>0.8449108426655551</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1535169551553612</v>
+        <v>0.1545269551553612</v>
       </c>
       <c r="C70">
-        <v>-11.30873872572491</v>
+        <v>-12.70533662280457</v>
       </c>
       <c r="D70">
-        <v>47.21526127427509</v>
+        <v>46.77666337719542</v>
       </c>
       <c r="E70">
-        <v>11.644</v>
+        <v>12.602</v>
       </c>
       <c r="F70">
-        <v>65.14399999999999</v>
+        <v>66.10199999999999</v>
       </c>
       <c r="G70">
         <v>6.62</v>
@@ -7015,37 +7015,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M70">
-        <v>9.5631392</v>
+        <v>9.7037736</v>
       </c>
       <c r="N70">
-        <v>-1.483139199999998</v>
+        <v>-1.623773599999998</v>
       </c>
       <c r="O70">
-        <v>-0.1334825279999999</v>
+        <v>-0.1461396239999998</v>
       </c>
       <c r="P70">
-        <v>-1.349656671999999</v>
+        <v>-1.477633975999998</v>
       </c>
       <c r="Q70">
-        <v>5.470343328000001</v>
+        <v>5.342366024000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1915117792237605</v>
+        <v>0.1962121591987205</v>
       </c>
       <c r="T70">
-        <v>2.120283932108856</v>
+        <v>2.188680187983335</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.07604197583989995</v>
+        <v>0.07493991821903184</v>
       </c>
       <c r="W70">
-        <v>0.1356370379467027</v>
+        <v>0.1357988200054462</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8449108426655551</v>
+        <v>0.8326657579892427</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1545269551553612</v>
+        <v>0.1555369551553612</v>
       </c>
       <c r="C71">
-        <v>-12.70533662280457</v>
+        <v>-14.09386096115605</v>
       </c>
       <c r="D71">
-        <v>46.77666337719542</v>
+        <v>46.34613903884394</v>
       </c>
       <c r="E71">
-        <v>12.602</v>
+        <v>13.56</v>
       </c>
       <c r="F71">
-        <v>66.10199999999999</v>
+        <v>67.05999999999999</v>
       </c>
       <c r="G71">
         <v>6.62</v>
@@ -7097,37 +7097,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M71">
-        <v>9.7037736</v>
+        <v>9.844408</v>
       </c>
       <c r="N71">
-        <v>-1.623773599999998</v>
+        <v>-1.764407999999998</v>
       </c>
       <c r="O71">
-        <v>-0.1461396239999998</v>
+        <v>-0.1587967199999998</v>
       </c>
       <c r="P71">
-        <v>-1.477633975999998</v>
+        <v>-1.605611279999998</v>
       </c>
       <c r="Q71">
-        <v>5.342366024000001</v>
+        <v>5.214388720000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1962121591987205</v>
+        <v>0.2012258978386778</v>
       </c>
       <c r="T71">
-        <v>2.188680187983335</v>
+        <v>2.261636194249447</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.07493991821903184</v>
+        <v>0.07386934795875995</v>
       </c>
       <c r="W71">
-        <v>0.1357988200054462</v>
+        <v>0.135955979719654</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8326657579892427</v>
+        <v>0.8207705328751107</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1555369551553612</v>
+        <v>0.1565469551553612</v>
       </c>
       <c r="C72">
-        <v>-14.09386096115605</v>
+        <v>-15.47453263067117</v>
       </c>
       <c r="D72">
-        <v>46.34613903884394</v>
+        <v>45.92346736932883</v>
       </c>
       <c r="E72">
-        <v>13.56</v>
+        <v>14.51800000000001</v>
       </c>
       <c r="F72">
-        <v>67.05999999999999</v>
+        <v>68.018</v>
       </c>
       <c r="G72">
         <v>6.62</v>
@@ -7179,37 +7179,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M72">
-        <v>9.844408</v>
+        <v>9.985042400000001</v>
       </c>
       <c r="N72">
-        <v>-1.764407999999998</v>
+        <v>-1.905042399999999</v>
       </c>
       <c r="O72">
-        <v>-0.1587967199999998</v>
+        <v>-0.1714538159999999</v>
       </c>
       <c r="P72">
-        <v>-1.605611279999998</v>
+        <v>-1.733588583999999</v>
       </c>
       <c r="Q72">
-        <v>5.214388720000001</v>
+        <v>5.086411416</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2012258978386778</v>
+        <v>0.2065854115572529</v>
       </c>
       <c r="T72">
-        <v>2.261636194249447</v>
+        <v>2.339623649223566</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.07386934795875995</v>
+        <v>0.07282893460722811</v>
       </c>
       <c r="W72">
-        <v>0.135955979719654</v>
+        <v>0.1361087123996589</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8207705328751107</v>
+        <v>0.8092103845247569</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1565469551553612</v>
+        <v>0.1971207017220338</v>
       </c>
       <c r="C73">
-        <v>-15.47453263067116</v>
+        <v>-28.74603042245872</v>
       </c>
       <c r="D73">
-        <v>45.92346736932883</v>
+        <v>33.60996957754127</v>
       </c>
       <c r="E73">
-        <v>14.51799999999999</v>
+        <v>15.47599999999999</v>
       </c>
       <c r="F73">
-        <v>68.01799999999999</v>
+        <v>68.97599999999998</v>
       </c>
       <c r="G73">
         <v>6.62</v>
@@ -7261,45 +7261,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M73">
-        <v>9.985042399999999</v>
+        <v>13.8503808</v>
       </c>
       <c r="N73">
-        <v>-1.905042399999997</v>
+        <v>-5.770380799999996</v>
       </c>
       <c r="O73">
-        <v>-0.1714538159999998</v>
+        <v>-0.5193342719999996</v>
       </c>
       <c r="P73">
-        <v>-1.733588583999998</v>
+        <v>-5.251046527999996</v>
       </c>
       <c r="Q73">
-        <v>5.086411416000002</v>
+        <v>1.568953472000003</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2065854115572529</v>
+        <v>0.2147696997081284</v>
       </c>
       <c r="T73">
-        <v>2.339623649223565</v>
+        <v>2.458715014070619</v>
       </c>
       <c r="U73">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.07282893460722813</v>
+        <v>0.05250397158755377</v>
       </c>
       <c r="W73">
-        <v>0.1361087123996589</v>
+        <v>0.1902572025052192</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.809210384524757</v>
+        <v>0.5833774620839307</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1971207017220338</v>
+        <v>0.1986707017220338</v>
       </c>
       <c r="C74">
-        <v>-28.74603042245872</v>
+        <v>-30.04481156795195</v>
       </c>
       <c r="D74">
-        <v>33.60996957754127</v>
+        <v>33.26918843204803</v>
       </c>
       <c r="E74">
-        <v>15.47599999999999</v>
+        <v>16.43399999999999</v>
       </c>
       <c r="F74">
-        <v>68.97599999999998</v>
+        <v>69.93399999999998</v>
       </c>
       <c r="G74">
         <v>6.62</v>
@@ -7343,37 +7343,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M74">
-        <v>13.8503808</v>
+        <v>14.0427472</v>
       </c>
       <c r="N74">
-        <v>-5.770380799999996</v>
+        <v>-5.962747199999995</v>
       </c>
       <c r="O74">
-        <v>-0.5193342719999996</v>
+        <v>-0.5366472479999995</v>
       </c>
       <c r="P74">
-        <v>-5.251046527999996</v>
+        <v>-5.426099951999996</v>
       </c>
       <c r="Q74">
-        <v>1.568953472000003</v>
+        <v>1.393900048000003</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2147696997081284</v>
+        <v>0.2210278367343554</v>
       </c>
       <c r="T74">
-        <v>2.458715014070619</v>
+        <v>2.549778533110271</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.05250397158755377</v>
+        <v>0.05178473910005304</v>
       </c>
       <c r="W74">
-        <v>0.1902572025052192</v>
+        <v>0.1904016243887094</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5833774620839307</v>
+        <v>0.5753859900005893</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1986707017220338</v>
+        <v>0.2002207017220338</v>
       </c>
       <c r="C75">
-        <v>-30.04481156795195</v>
+        <v>-31.3367515222108</v>
       </c>
       <c r="D75">
-        <v>33.26918843204803</v>
+        <v>32.93524847778919</v>
       </c>
       <c r="E75">
-        <v>16.43399999999999</v>
+        <v>17.39199999999999</v>
       </c>
       <c r="F75">
-        <v>69.93399999999998</v>
+        <v>70.89199999999998</v>
       </c>
       <c r="G75">
         <v>6.62</v>
@@ -7425,37 +7425,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M75">
-        <v>14.0427472</v>
+        <v>14.2351136</v>
       </c>
       <c r="N75">
-        <v>-5.962747199999995</v>
+        <v>-6.155113599999995</v>
       </c>
       <c r="O75">
-        <v>-0.5366472479999995</v>
+        <v>-0.5539602239999994</v>
       </c>
       <c r="P75">
-        <v>-5.426099951999996</v>
+        <v>-5.601153375999996</v>
       </c>
       <c r="Q75">
-        <v>1.393900048000003</v>
+        <v>1.218846624000004</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2210278367343554</v>
+        <v>0.2277673689164459</v>
       </c>
       <c r="T75">
-        <v>2.549778533110271</v>
+        <v>2.647846938229897</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.05178473910005304</v>
+        <v>0.0510849453284307</v>
       </c>
       <c r="W75">
-        <v>0.1904016243887094</v>
+        <v>0.1905421429780511</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5753859900005893</v>
+        <v>0.56761050364923</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2002207017220338</v>
+        <v>0.2017707017220338</v>
       </c>
       <c r="C76">
-        <v>-31.3367515222108</v>
+        <v>-32.62205424366392</v>
       </c>
       <c r="D76">
-        <v>32.93524847778919</v>
+        <v>32.60794575633608</v>
       </c>
       <c r="E76">
-        <v>17.39199999999999</v>
+        <v>18.35</v>
       </c>
       <c r="F76">
-        <v>70.89199999999998</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G76">
         <v>6.62</v>
@@ -7507,37 +7507,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M76">
-        <v>14.2351136</v>
+        <v>14.42748</v>
       </c>
       <c r="N76">
-        <v>-6.155113599999995</v>
+        <v>-6.347479999999997</v>
       </c>
       <c r="O76">
-        <v>-0.5539602239999994</v>
+        <v>-0.5712731999999997</v>
       </c>
       <c r="P76">
-        <v>-5.601153375999996</v>
+        <v>-5.776206799999998</v>
       </c>
       <c r="Q76">
-        <v>1.218846624000004</v>
+        <v>1.043793200000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2277673689164459</v>
+        <v>0.2350460636731038</v>
       </c>
       <c r="T76">
-        <v>2.647846938229897</v>
+        <v>2.753760815759093</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.0510849453284307</v>
+        <v>0.05040381272405161</v>
       </c>
       <c r="W76">
-        <v>0.1905421429780511</v>
+        <v>0.1906789144050104</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.56761050364923</v>
+        <v>0.5600423636005736</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2017707017220338</v>
+        <v>0.2033207017220338</v>
       </c>
       <c r="C77">
-        <v>-32.62205424366392</v>
+        <v>-33.9009156629554</v>
       </c>
       <c r="D77">
-        <v>32.60794575633608</v>
+        <v>32.2870843370446</v>
       </c>
       <c r="E77">
-        <v>18.35</v>
+        <v>19.308</v>
       </c>
       <c r="F77">
-        <v>71.84999999999999</v>
+        <v>72.80799999999999</v>
       </c>
       <c r="G77">
         <v>6.62</v>
@@ -7589,37 +7589,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M77">
-        <v>14.42748</v>
+        <v>14.6198464</v>
       </c>
       <c r="N77">
-        <v>-6.347479999999997</v>
+        <v>-6.539846399999997</v>
       </c>
       <c r="O77">
-        <v>-0.5712731999999997</v>
+        <v>-0.5885861759999996</v>
       </c>
       <c r="P77">
-        <v>-5.776206799999998</v>
+        <v>-5.951260223999997</v>
       </c>
       <c r="Q77">
-        <v>1.043793200000001</v>
+        <v>0.8687397760000026</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2350460636731038</v>
+        <v>0.2429313163261498</v>
       </c>
       <c r="T77">
-        <v>2.753760815759093</v>
+        <v>2.868500849749056</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.05040381272405161</v>
+        <v>0.04974060466189304</v>
       </c>
       <c r="W77">
-        <v>0.1906789144050104</v>
+        <v>0.1908120865838919</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5600423636005736</v>
+        <v>0.5526733851321449</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2033207017220338</v>
+        <v>0.2048707017220338</v>
       </c>
       <c r="C78">
-        <v>-33.9009156629554</v>
+        <v>-35.17352407406222</v>
       </c>
       <c r="D78">
-        <v>32.2870843370446</v>
+        <v>31.97247592593777</v>
       </c>
       <c r="E78">
-        <v>19.308</v>
+        <v>20.266</v>
       </c>
       <c r="F78">
-        <v>72.80799999999999</v>
+        <v>73.76599999999999</v>
       </c>
       <c r="G78">
         <v>6.62</v>
@@ -7671,37 +7671,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M78">
-        <v>14.6198464</v>
+        <v>14.8122128</v>
       </c>
       <c r="N78">
-        <v>-6.539846399999997</v>
+        <v>-6.732212799999997</v>
       </c>
       <c r="O78">
-        <v>-0.5885861759999996</v>
+        <v>-0.6058991519999998</v>
       </c>
       <c r="P78">
-        <v>-5.951260223999997</v>
+        <v>-6.126313647999997</v>
       </c>
       <c r="Q78">
-        <v>0.8687397760000026</v>
+        <v>0.6936863520000021</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2429313163261498</v>
+        <v>0.2515022431229389</v>
       </c>
       <c r="T78">
-        <v>2.868500849749056</v>
+        <v>2.993218277999014</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.04974060466189304</v>
+        <v>0.04909462278316715</v>
       </c>
       <c r="W78">
-        <v>0.1908120865838919</v>
+        <v>0.1909417997451401</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5526733851321449</v>
+        <v>0.5454958087018573</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2048707017220338</v>
+        <v>0.2064207017220338</v>
       </c>
       <c r="C79">
-        <v>-35.17352407406222</v>
+        <v>-36.44006050276595</v>
       </c>
       <c r="D79">
-        <v>31.97247592593777</v>
+        <v>31.66393949723404</v>
       </c>
       <c r="E79">
-        <v>20.266</v>
+        <v>21.224</v>
       </c>
       <c r="F79">
-        <v>73.76599999999999</v>
+        <v>74.72399999999999</v>
       </c>
       <c r="G79">
         <v>6.62</v>
@@ -7753,37 +7753,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M79">
-        <v>14.8122128</v>
+        <v>15.0045792</v>
       </c>
       <c r="N79">
-        <v>-6.732212799999997</v>
+        <v>-6.924579199999997</v>
       </c>
       <c r="O79">
-        <v>-0.6058991519999998</v>
+        <v>-0.6232121279999997</v>
       </c>
       <c r="P79">
-        <v>-6.126313647999997</v>
+        <v>-6.301367071999997</v>
       </c>
       <c r="Q79">
-        <v>0.6936863520000021</v>
+        <v>0.5186329280000024</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2515022431229389</v>
+        <v>0.2608523450830725</v>
       </c>
       <c r="T79">
-        <v>2.993218277999014</v>
+        <v>3.129273654271697</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.04909462278316715</v>
+        <v>0.04846520454235733</v>
       </c>
       <c r="W79">
-        <v>0.1909417997451401</v>
+        <v>0.1910681869278947</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5454958087018573</v>
+        <v>0.5385022726928592</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2064207017220338</v>
+        <v>0.2079707017220338</v>
       </c>
       <c r="C80">
-        <v>-36.44006050276595</v>
+        <v>-37.70069905399351</v>
       </c>
       <c r="D80">
-        <v>31.66393949723404</v>
+        <v>31.36130094600648</v>
       </c>
       <c r="E80">
-        <v>21.224</v>
+        <v>22.182</v>
       </c>
       <c r="F80">
-        <v>74.72399999999999</v>
+        <v>75.68199999999999</v>
       </c>
       <c r="G80">
         <v>6.62</v>
@@ -7835,37 +7835,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M80">
-        <v>15.0045792</v>
+        <v>15.1969456</v>
       </c>
       <c r="N80">
-        <v>-6.924579199999997</v>
+        <v>-7.116945599999996</v>
       </c>
       <c r="O80">
-        <v>-0.6232121279999997</v>
+        <v>-0.6405251039999996</v>
       </c>
       <c r="P80">
-        <v>-6.301367071999997</v>
+        <v>-6.476420495999996</v>
       </c>
       <c r="Q80">
-        <v>0.5186329280000024</v>
+        <v>0.3435795040000036</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2608523450830725</v>
+        <v>0.2710929329441712</v>
       </c>
       <c r="T80">
-        <v>3.129273654271697</v>
+        <v>3.278286685427492</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.04846520454235733</v>
+        <v>0.04785172094055534</v>
       </c>
       <c r="W80">
-        <v>0.1910681869278947</v>
+        <v>0.1911913744351365</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5385022726928592</v>
+        <v>0.5316857882283926</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2079707017220338</v>
+        <v>0.2095207017220338</v>
       </c>
       <c r="C81">
-        <v>-37.70069905399351</v>
+        <v>-38.95560723942776</v>
       </c>
       <c r="D81">
-        <v>31.36130094600648</v>
+        <v>31.06439276057223</v>
       </c>
       <c r="E81">
-        <v>22.182</v>
+        <v>23.13999999999999</v>
       </c>
       <c r="F81">
-        <v>75.68199999999999</v>
+        <v>76.63999999999999</v>
       </c>
       <c r="G81">
         <v>6.62</v>
@@ -7917,37 +7917,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M81">
-        <v>15.1969456</v>
+        <v>15.389312</v>
       </c>
       <c r="N81">
-        <v>-7.116945599999996</v>
+        <v>-7.309311999999997</v>
       </c>
       <c r="O81">
-        <v>-0.6405251039999996</v>
+        <v>-0.6578380799999997</v>
       </c>
       <c r="P81">
-        <v>-6.476420495999996</v>
+        <v>-6.651473919999997</v>
       </c>
       <c r="Q81">
-        <v>0.3435795040000036</v>
+        <v>0.1685260800000021</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2710929329441712</v>
+        <v>0.2823575795913797</v>
       </c>
       <c r="T81">
-        <v>3.278286685427492</v>
+        <v>3.442201019698866</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.04785172094055534</v>
+        <v>0.04725357442879839</v>
       </c>
       <c r="W81">
-        <v>0.1911913744351365</v>
+        <v>0.1913114822546973</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5316857882283926</v>
+        <v>0.5250397158755377</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2095207017220338</v>
+        <v>0.2110707017220338</v>
       </c>
       <c r="C82">
-        <v>-38.95560723942776</v>
+        <v>-40.2049462866829</v>
       </c>
       <c r="D82">
-        <v>31.06439276057223</v>
+        <v>30.77305371331708</v>
       </c>
       <c r="E82">
-        <v>23.13999999999999</v>
+        <v>24.09799999999999</v>
       </c>
       <c r="F82">
-        <v>76.63999999999999</v>
+        <v>77.59799999999998</v>
       </c>
       <c r="G82">
         <v>6.62</v>
@@ -7999,37 +7999,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M82">
-        <v>15.389312</v>
+        <v>15.5816784</v>
       </c>
       <c r="N82">
-        <v>-7.309311999999997</v>
+        <v>-7.501678399999996</v>
       </c>
       <c r="O82">
-        <v>-0.6578380799999997</v>
+        <v>-0.6751510559999996</v>
       </c>
       <c r="P82">
-        <v>-6.651473919999997</v>
+        <v>-6.826527343999996</v>
       </c>
       <c r="Q82">
-        <v>0.1685260800000021</v>
+        <v>-0.00652734399999666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2823575795913797</v>
+        <v>0.2948079785172419</v>
       </c>
       <c r="T82">
-        <v>3.442201019698866</v>
+        <v>3.62336949441986</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.04725357442879839</v>
+        <v>0.04667019696671447</v>
       </c>
       <c r="W82">
-        <v>0.1913114822546973</v>
+        <v>0.1914286244490837</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5250397158755377</v>
+        <v>0.5185577440746052</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2110707017220338</v>
+        <v>0.2126207017220338</v>
       </c>
       <c r="C83">
-        <v>-40.2049462866829</v>
+        <v>-41.44887143124393</v>
       </c>
       <c r="D83">
-        <v>30.77305371331708</v>
+        <v>30.48712856875607</v>
       </c>
       <c r="E83">
-        <v>24.09799999999999</v>
+        <v>25.056</v>
       </c>
       <c r="F83">
-        <v>77.59799999999998</v>
+        <v>78.556</v>
       </c>
       <c r="G83">
         <v>6.62</v>
@@ -8081,37 +8081,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M83">
-        <v>15.5816784</v>
+        <v>15.7740448</v>
       </c>
       <c r="N83">
-        <v>-7.501678399999996</v>
+        <v>-7.694044799999999</v>
       </c>
       <c r="O83">
-        <v>-0.6751510559999996</v>
+        <v>-0.6924640319999998</v>
       </c>
       <c r="P83">
-        <v>-6.826527343999996</v>
+        <v>-7.001580767999998</v>
       </c>
       <c r="Q83">
-        <v>-0.00652734399999666</v>
+        <v>-0.181580767999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2948079785172419</v>
+        <v>0.3086417551015331</v>
       </c>
       <c r="T83">
-        <v>3.62336949441986</v>
+        <v>3.824667799665408</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.04667019696671447</v>
+        <v>0.04610104822321794</v>
       </c>
       <c r="W83">
-        <v>0.1914286244490837</v>
+        <v>0.1915429095167779</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5185577440746052</v>
+        <v>0.512233869146866</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2126207017220338</v>
+        <v>0.2141707017220338</v>
       </c>
       <c r="C84">
-        <v>-41.44887143124393</v>
+        <v>-42.68753219228051</v>
       </c>
       <c r="D84">
-        <v>30.48712856875607</v>
+        <v>30.20646780771948</v>
       </c>
       <c r="E84">
-        <v>25.056</v>
+        <v>26.014</v>
       </c>
       <c r="F84">
-        <v>78.556</v>
+        <v>79.514</v>
       </c>
       <c r="G84">
         <v>6.62</v>
@@ -8163,37 +8163,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M84">
-        <v>15.7740448</v>
+        <v>15.9664112</v>
       </c>
       <c r="N84">
-        <v>-7.694044799999999</v>
+        <v>-7.886411199999998</v>
       </c>
       <c r="O84">
-        <v>-0.6924640319999998</v>
+        <v>-0.7097770079999998</v>
       </c>
       <c r="P84">
-        <v>-7.001580767999998</v>
+        <v>-7.176634191999998</v>
       </c>
       <c r="Q84">
-        <v>-0.181580767999999</v>
+        <v>-0.3566341919999987</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3086417551015331</v>
+        <v>0.324103034813388</v>
       </c>
       <c r="T84">
-        <v>3.824667799665408</v>
+        <v>4.049648258469256</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.04610104822321794</v>
+        <v>0.04554561390727556</v>
       </c>
       <c r="W84">
-        <v>0.1915429095167779</v>
+        <v>0.1916544407274191</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.512233869146866</v>
+        <v>0.5060623767475061</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2141707017220338</v>
+        <v>0.2157207017220338</v>
       </c>
       <c r="C85">
-        <v>-42.68753219228051</v>
+        <v>-43.92107263336554</v>
       </c>
       <c r="D85">
-        <v>30.20646780771948</v>
+        <v>29.93092736663445</v>
       </c>
       <c r="E85">
-        <v>26.014</v>
+        <v>26.972</v>
       </c>
       <c r="F85">
-        <v>79.514</v>
+        <v>80.47199999999999</v>
       </c>
       <c r="G85">
         <v>6.62</v>
@@ -8245,37 +8245,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M85">
-        <v>15.9664112</v>
+        <v>16.1587776</v>
       </c>
       <c r="N85">
-        <v>-7.886411199999998</v>
+        <v>-8.078777599999999</v>
       </c>
       <c r="O85">
-        <v>-0.7097770079999998</v>
+        <v>-0.7270899839999998</v>
       </c>
       <c r="P85">
-        <v>-7.176634191999998</v>
+        <v>-7.351687615999999</v>
       </c>
       <c r="Q85">
-        <v>-0.3566341919999987</v>
+        <v>-0.5316876159999993</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.324103034813388</v>
+        <v>0.3414969744892248</v>
       </c>
       <c r="T85">
-        <v>4.049648258469256</v>
+        <v>4.302751274623585</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.04554561390727556</v>
+        <v>0.04500340421790323</v>
       </c>
       <c r="W85">
-        <v>0.1916544407274191</v>
+        <v>0.191763316433045</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5060623767475061</v>
+        <v>0.5000378246433692</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2157207017220338</v>
+        <v>0.2472966017204288</v>
       </c>
       <c r="C86">
-        <v>-43.92107263336552</v>
+        <v>-49.56945431384354</v>
       </c>
       <c r="D86">
-        <v>29.93092736663446</v>
+        <v>25.24054568615644</v>
       </c>
       <c r="E86">
-        <v>26.97199999999999</v>
+        <v>27.92999999999999</v>
       </c>
       <c r="F86">
-        <v>80.47199999999998</v>
+        <v>81.42999999999998</v>
       </c>
       <c r="G86">
         <v>6.62</v>
@@ -8327,45 +8327,45 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M86">
-        <v>16.1587776</v>
+        <v>19.201194</v>
       </c>
       <c r="N86">
-        <v>-8.078777599999995</v>
+        <v>-11.121194</v>
       </c>
       <c r="O86">
-        <v>-0.7270899839999996</v>
+        <v>-1.00090746</v>
       </c>
       <c r="P86">
-        <v>-7.351687615999996</v>
+        <v>-10.12028654</v>
       </c>
       <c r="Q86">
-        <v>-0.5316876159999966</v>
+        <v>-3.300286539999996</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3414969744892247</v>
+        <v>0.3630494394444733</v>
       </c>
       <c r="T86">
-        <v>4.302751274623582</v>
+        <v>4.616365900602299</v>
       </c>
       <c r="U86">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04500340421790323</v>
+        <v>0.03787264479490183</v>
       </c>
       <c r="W86">
-        <v>0.191763316433045</v>
+        <v>0.2268696303573622</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5000378246433692</v>
+        <v>0.4208071643877981</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2472966017204288</v>
+        <v>0.2491966017204288</v>
       </c>
       <c r="C87">
-        <v>-49.56945431384354</v>
+        <v>-50.7632352285592</v>
       </c>
       <c r="D87">
-        <v>25.24054568615644</v>
+        <v>25.00476477144079</v>
       </c>
       <c r="E87">
-        <v>27.92999999999999</v>
+        <v>28.888</v>
       </c>
       <c r="F87">
-        <v>81.42999999999998</v>
+        <v>82.38799999999999</v>
       </c>
       <c r="G87">
         <v>6.62</v>
@@ -8409,37 +8409,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M87">
-        <v>19.201194</v>
+        <v>19.4270904</v>
       </c>
       <c r="N87">
-        <v>-11.121194</v>
+        <v>-11.3470904</v>
       </c>
       <c r="O87">
-        <v>-1.00090746</v>
+        <v>-1.021238136</v>
       </c>
       <c r="P87">
-        <v>-10.12028654</v>
+        <v>-10.325852264</v>
       </c>
       <c r="Q87">
-        <v>-3.300286539999996</v>
+        <v>-3.505852263999997</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3630494394444733</v>
+        <v>0.3857101136905071</v>
       </c>
       <c r="T87">
-        <v>4.616365900602299</v>
+        <v>4.946106322073891</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03787264479490183</v>
+        <v>0.03743226520426343</v>
       </c>
       <c r="W87">
-        <v>0.2268696303573622</v>
+        <v>0.2269734718648347</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4208071643877981</v>
+        <v>0.4159140578251493</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2491966017204288</v>
+        <v>0.2510966017204289</v>
       </c>
       <c r="C88">
-        <v>-50.7632352285592</v>
+        <v>-51.95265188459541</v>
       </c>
       <c r="D88">
-        <v>25.00476477144079</v>
+        <v>24.77334811540458</v>
       </c>
       <c r="E88">
-        <v>28.888</v>
+        <v>29.846</v>
       </c>
       <c r="F88">
-        <v>82.38799999999999</v>
+        <v>83.34599999999999</v>
       </c>
       <c r="G88">
         <v>6.62</v>
@@ -8491,37 +8491,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M88">
-        <v>19.4270904</v>
+        <v>19.6529868</v>
       </c>
       <c r="N88">
-        <v>-11.3470904</v>
+        <v>-11.5729868</v>
       </c>
       <c r="O88">
-        <v>-1.021238136</v>
+        <v>-1.041568812</v>
       </c>
       <c r="P88">
-        <v>-10.325852264</v>
+        <v>-10.531417988</v>
       </c>
       <c r="Q88">
-        <v>-3.505852263999997</v>
+        <v>-3.711417987999996</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3857101136905071</v>
+        <v>0.4118570455128538</v>
       </c>
       <c r="T88">
-        <v>4.946106322073891</v>
+        <v>5.326576039156499</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03743226520426343</v>
+        <v>0.03700200928237535</v>
       </c>
       <c r="W88">
-        <v>0.2269734718648347</v>
+        <v>0.2270749262112159</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4159140578251493</v>
+        <v>0.4111334364708372</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2510966017204289</v>
+        <v>0.2529966017204288</v>
       </c>
       <c r="C89">
-        <v>-51.95265188459541</v>
+        <v>-53.13782434316101</v>
       </c>
       <c r="D89">
-        <v>24.77334811540458</v>
+        <v>24.54617565683898</v>
       </c>
       <c r="E89">
-        <v>29.846</v>
+        <v>30.80399999999999</v>
       </c>
       <c r="F89">
-        <v>83.34599999999999</v>
+        <v>84.30399999999999</v>
       </c>
       <c r="G89">
         <v>6.62</v>
@@ -8573,37 +8573,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M89">
-        <v>19.6529868</v>
+        <v>19.8788832</v>
       </c>
       <c r="N89">
-        <v>-11.5729868</v>
+        <v>-11.7988832</v>
       </c>
       <c r="O89">
-        <v>-1.041568812</v>
+        <v>-1.061899487999999</v>
       </c>
       <c r="P89">
-        <v>-10.531417988</v>
+        <v>-10.736983712</v>
       </c>
       <c r="Q89">
-        <v>-3.711417987999996</v>
+        <v>-3.916983711999996</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4118570455128538</v>
+        <v>0.4423617993055917</v>
       </c>
       <c r="T89">
-        <v>5.326576039156499</v>
+        <v>5.770457375752875</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03700200928237535</v>
+        <v>0.03658153190416654</v>
       </c>
       <c r="W89">
-        <v>0.2270749262112159</v>
+        <v>0.2271740747769975</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4111334364708372</v>
+        <v>0.4064614656018505</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2529966017204288</v>
+        <v>0.2548966017204289</v>
       </c>
       <c r="C90">
-        <v>-53.13782434316101</v>
+        <v>-54.31886830161974</v>
       </c>
       <c r="D90">
-        <v>24.54617565683898</v>
+        <v>24.32313169838024</v>
       </c>
       <c r="E90">
-        <v>30.80399999999999</v>
+        <v>31.76199999999999</v>
       </c>
       <c r="F90">
-        <v>84.30399999999999</v>
+        <v>85.26199999999999</v>
       </c>
       <c r="G90">
         <v>6.62</v>
@@ -8655,37 +8655,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M90">
-        <v>19.8788832</v>
+        <v>20.1047796</v>
       </c>
       <c r="N90">
-        <v>-11.7988832</v>
+        <v>-12.0247796</v>
       </c>
       <c r="O90">
-        <v>-1.061899487999999</v>
+        <v>-1.082230164</v>
       </c>
       <c r="P90">
-        <v>-10.736983712</v>
+        <v>-10.94254943599999</v>
       </c>
       <c r="Q90">
-        <v>-3.916983711999996</v>
+        <v>-4.122549435999995</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4423617993055917</v>
+        <v>0.4784128719697365</v>
       </c>
       <c r="T90">
-        <v>5.770457375752875</v>
+        <v>6.295044409912228</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03658153190416654</v>
+        <v>0.03617050345580512</v>
       </c>
       <c r="W90">
-        <v>0.2271740747769975</v>
+        <v>0.2272709952851212</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4064614656018505</v>
+        <v>0.4018944828422791</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2548966017204289</v>
+        <v>0.2567966017204288</v>
       </c>
       <c r="C91">
-        <v>-54.31886830161974</v>
+        <v>-55.49589528996979</v>
       </c>
       <c r="D91">
-        <v>24.32313169838024</v>
+        <v>24.10410471003019</v>
       </c>
       <c r="E91">
-        <v>31.76199999999999</v>
+        <v>32.71999999999999</v>
       </c>
       <c r="F91">
-        <v>85.26199999999999</v>
+        <v>86.21999999999998</v>
       </c>
       <c r="G91">
         <v>6.62</v>
@@ -8737,37 +8737,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M91">
-        <v>20.1047796</v>
+        <v>20.330676</v>
       </c>
       <c r="N91">
-        <v>-12.0247796</v>
+        <v>-12.250676</v>
       </c>
       <c r="O91">
-        <v>-1.082230164</v>
+        <v>-1.10256084</v>
       </c>
       <c r="P91">
-        <v>-10.94254943599999</v>
+        <v>-11.14811516</v>
       </c>
       <c r="Q91">
-        <v>-4.122549435999995</v>
+        <v>-4.328115159999997</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4784128719697365</v>
+        <v>0.5216741591667101</v>
       </c>
       <c r="T91">
-        <v>6.295044409912228</v>
+        <v>6.924548850903451</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03617050345580512</v>
+        <v>0.03576860897296284</v>
       </c>
       <c r="W91">
-        <v>0.2272709952851212</v>
+        <v>0.2273657620041754</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4018944828422791</v>
+        <v>0.397428988588476</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2567966017204288</v>
+        <v>0.2586966017204288</v>
       </c>
       <c r="C92">
-        <v>-55.49589528996979</v>
+        <v>-56.66901285680253</v>
       </c>
       <c r="D92">
-        <v>24.10410471003019</v>
+        <v>23.88898714319745</v>
       </c>
       <c r="E92">
-        <v>32.71999999999999</v>
+        <v>33.67799999999999</v>
       </c>
       <c r="F92">
-        <v>86.21999999999998</v>
+        <v>87.17799999999998</v>
       </c>
       <c r="G92">
         <v>6.62</v>
@@ -8819,37 +8819,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M92">
-        <v>20.330676</v>
+        <v>20.5565724</v>
       </c>
       <c r="N92">
-        <v>-12.250676</v>
+        <v>-12.47657239999999</v>
       </c>
       <c r="O92">
-        <v>-1.10256084</v>
+        <v>-1.122891515999999</v>
       </c>
       <c r="P92">
-        <v>-11.14811516</v>
+        <v>-11.353680884</v>
       </c>
       <c r="Q92">
-        <v>-4.328115159999997</v>
+        <v>-4.533680883999996</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5216741591667101</v>
+        <v>0.574549065740789</v>
       </c>
       <c r="T92">
-        <v>6.924548850903451</v>
+        <v>7.693943167670501</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03576860897296284</v>
+        <v>0.03537554733589731</v>
       </c>
       <c r="W92">
-        <v>0.2273657620041754</v>
+        <v>0.2274584459381954</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.397428988588476</v>
+        <v>0.3930616370655258</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2586966017204288</v>
+        <v>0.2605966017204288</v>
       </c>
       <c r="C93">
-        <v>-56.66901285680253</v>
+        <v>-57.83832474539168</v>
       </c>
       <c r="D93">
-        <v>23.88898714319745</v>
+        <v>23.6776752546083</v>
       </c>
       <c r="E93">
-        <v>33.67799999999999</v>
+        <v>34.63599999999999</v>
       </c>
       <c r="F93">
-        <v>87.17799999999998</v>
+        <v>88.13599999999998</v>
       </c>
       <c r="G93">
         <v>6.62</v>
@@ -8901,37 +8901,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M93">
-        <v>20.5565724</v>
+        <v>20.7824688</v>
       </c>
       <c r="N93">
-        <v>-12.47657239999999</v>
+        <v>-12.70246879999999</v>
       </c>
       <c r="O93">
-        <v>-1.122891515999999</v>
+        <v>-1.143222191999999</v>
       </c>
       <c r="P93">
-        <v>-11.353680884</v>
+        <v>-11.559246608</v>
       </c>
       <c r="Q93">
-        <v>-4.533680883999996</v>
+        <v>-4.739246607999996</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.574549065740789</v>
+        <v>0.6406426989583878</v>
       </c>
       <c r="T93">
-        <v>7.693943167670501</v>
+        <v>8.655686063629316</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03537554733589731</v>
+        <v>0.03499103051702886</v>
       </c>
       <c r="W93">
-        <v>0.2274584459381954</v>
+        <v>0.2275491150040846</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3930616370655258</v>
+        <v>0.3887892279669874</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2605966017204288</v>
+        <v>0.2624966017204289</v>
       </c>
       <c r="C94">
-        <v>-57.83832474539168</v>
+        <v>-59.00393106051887</v>
       </c>
       <c r="D94">
-        <v>23.6776752546083</v>
+        <v>23.47006893948113</v>
       </c>
       <c r="E94">
-        <v>34.63599999999999</v>
+        <v>35.594</v>
       </c>
       <c r="F94">
-        <v>88.13599999999998</v>
+        <v>89.09399999999999</v>
       </c>
       <c r="G94">
         <v>6.62</v>
@@ -8983,37 +8983,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M94">
-        <v>20.7824688</v>
+        <v>21.0083652</v>
       </c>
       <c r="N94">
-        <v>-12.70246879999999</v>
+        <v>-12.9283652</v>
       </c>
       <c r="O94">
-        <v>-1.143222191999999</v>
+        <v>-1.163552868</v>
       </c>
       <c r="P94">
-        <v>-11.559246608</v>
+        <v>-11.764812332</v>
       </c>
       <c r="Q94">
-        <v>-4.739246607999996</v>
+        <v>-4.944812331999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6406426989583878</v>
+        <v>0.7256202273810147</v>
       </c>
       <c r="T94">
-        <v>8.655686063629316</v>
+        <v>9.892212644147792</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03499103051702886</v>
+        <v>0.03461478287706081</v>
       </c>
       <c r="W94">
-        <v>0.2275491150040846</v>
+        <v>0.2276378341975891</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3887892279669874</v>
+        <v>0.3846086986340089</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2624966017204289</v>
+        <v>0.2643966017204288</v>
       </c>
       <c r="C95">
-        <v>-59.00393106051887</v>
+        <v>-60.16592842659889</v>
       </c>
       <c r="D95">
-        <v>23.47006893948113</v>
+        <v>23.2660715734011</v>
       </c>
       <c r="E95">
-        <v>35.594</v>
+        <v>36.552</v>
       </c>
       <c r="F95">
-        <v>89.09399999999999</v>
+        <v>90.05199999999999</v>
       </c>
       <c r="G95">
         <v>6.62</v>
@@ -9065,37 +9065,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M95">
-        <v>21.0083652</v>
+        <v>21.2342616</v>
       </c>
       <c r="N95">
-        <v>-12.9283652</v>
+        <v>-13.1542616</v>
       </c>
       <c r="O95">
-        <v>-1.163552868</v>
+        <v>-1.183883544</v>
       </c>
       <c r="P95">
-        <v>-11.764812332</v>
+        <v>-11.970378056</v>
       </c>
       <c r="Q95">
-        <v>-4.944812331999999</v>
+        <v>-5.150378055999998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7256202273810147</v>
+        <v>0.838923598611184</v>
       </c>
       <c r="T95">
-        <v>9.892212644147792</v>
+        <v>11.54091475150576</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03461478287706081</v>
+        <v>0.03424654050602825</v>
       </c>
       <c r="W95">
-        <v>0.2276378341975891</v>
+        <v>0.2277246657486786</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3846086986340089</v>
+        <v>0.3805171167336472</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2643966017204288</v>
+        <v>0.2662966017204288</v>
       </c>
       <c r="C96">
-        <v>-60.16592842659889</v>
+        <v>-61.32441013763002</v>
       </c>
       <c r="D96">
-        <v>23.2660715734011</v>
+        <v>23.06558986236997</v>
       </c>
       <c r="E96">
-        <v>36.552</v>
+        <v>37.51</v>
       </c>
       <c r="F96">
-        <v>90.05199999999999</v>
+        <v>91.00999999999999</v>
       </c>
       <c r="G96">
         <v>6.62</v>
@@ -9147,37 +9147,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M96">
-        <v>21.2342616</v>
+        <v>21.460158</v>
       </c>
       <c r="N96">
-        <v>-13.1542616</v>
+        <v>-13.380158</v>
       </c>
       <c r="O96">
-        <v>-1.183883544</v>
+        <v>-1.20421422</v>
       </c>
       <c r="P96">
-        <v>-11.970378056</v>
+        <v>-12.17594378</v>
       </c>
       <c r="Q96">
-        <v>-5.150378055999998</v>
+        <v>-5.35594378</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.838923598611184</v>
+        <v>0.9975483183334214</v>
       </c>
       <c r="T96">
-        <v>11.54091475150576</v>
+        <v>13.84909770180692</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03424654050602825</v>
+        <v>0.03388605060596479</v>
       </c>
       <c r="W96">
-        <v>0.2277246657486786</v>
+        <v>0.2278096692671135</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3805171167336472</v>
+        <v>0.3765116733996088</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2662966017204288</v>
+        <v>0.2681966017204289</v>
       </c>
       <c r="C97">
-        <v>-61.32441013763002</v>
+        <v>-62.47946629945751</v>
       </c>
       <c r="D97">
-        <v>23.06558986236997</v>
+        <v>22.86853370054248</v>
       </c>
       <c r="E97">
-        <v>37.51</v>
+        <v>38.468</v>
       </c>
       <c r="F97">
-        <v>91.00999999999999</v>
+        <v>91.96799999999999</v>
       </c>
       <c r="G97">
         <v>6.62</v>
@@ -9229,37 +9229,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M97">
-        <v>21.460158</v>
+        <v>21.6860544</v>
       </c>
       <c r="N97">
-        <v>-13.380158</v>
+        <v>-13.6060544</v>
       </c>
       <c r="O97">
-        <v>-1.20421422</v>
+        <v>-1.224544896</v>
       </c>
       <c r="P97">
-        <v>-12.17594378</v>
+        <v>-12.381509504</v>
       </c>
       <c r="Q97">
-        <v>-5.35594378</v>
+        <v>-5.561509503999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9975483183334214</v>
+        <v>1.235485397916777</v>
       </c>
       <c r="T97">
-        <v>13.84909770180692</v>
+        <v>17.31137212725865</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03388605060596479</v>
+        <v>0.03353307091215266</v>
       </c>
       <c r="W97">
-        <v>0.2278096692671135</v>
+        <v>0.2278929018789144</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3765116733996088</v>
+        <v>0.3725896768016962</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2681966017204289</v>
+        <v>0.2700966017204288</v>
       </c>
       <c r="C98">
-        <v>-62.47946629945749</v>
+        <v>-63.63118396480665</v>
       </c>
       <c r="D98">
-        <v>22.86853370054248</v>
+        <v>22.67481603519333</v>
       </c>
       <c r="E98">
-        <v>38.46799999999998</v>
+        <v>39.42599999999999</v>
       </c>
       <c r="F98">
-        <v>91.96799999999998</v>
+        <v>92.92599999999999</v>
       </c>
       <c r="G98">
         <v>6.62</v>
@@ -9311,37 +9311,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M98">
-        <v>21.6860544</v>
+        <v>21.9119508</v>
       </c>
       <c r="N98">
-        <v>-13.60605439999999</v>
+        <v>-13.8319508</v>
       </c>
       <c r="O98">
-        <v>-1.224544895999999</v>
+        <v>-1.244875572</v>
       </c>
       <c r="P98">
-        <v>-12.38150950399999</v>
+        <v>-12.587075228</v>
       </c>
       <c r="Q98">
-        <v>-5.561509503999996</v>
+        <v>-5.767075227999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.235485397916774</v>
+        <v>1.632047197222366</v>
       </c>
       <c r="T98">
-        <v>17.31137212725861</v>
+        <v>23.08182950301148</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03353307091215266</v>
+        <v>0.0331873691501717</v>
       </c>
       <c r="W98">
-        <v>0.2278929018789144</v>
+        <v>0.2279744183543895</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3725896768016963</v>
+        <v>0.3687485461130189</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2700966017204288</v>
+        <v>0.2719966017204288</v>
       </c>
       <c r="C99">
-        <v>-63.63118396480665</v>
+        <v>-64.77964726151045</v>
       </c>
       <c r="D99">
-        <v>22.67481603519333</v>
+        <v>22.48435273848954</v>
       </c>
       <c r="E99">
-        <v>39.42599999999999</v>
+        <v>40.38399999999999</v>
       </c>
       <c r="F99">
-        <v>92.92599999999999</v>
+        <v>93.88399999999999</v>
       </c>
       <c r="G99">
         <v>6.62</v>
@@ -9393,37 +9393,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M99">
-        <v>21.9119508</v>
+        <v>22.1378472</v>
       </c>
       <c r="N99">
-        <v>-13.8319508</v>
+        <v>-14.05784719999999</v>
       </c>
       <c r="O99">
-        <v>-1.244875572</v>
+        <v>-1.265206247999999</v>
       </c>
       <c r="P99">
-        <v>-12.587075228</v>
+        <v>-12.79264095199999</v>
       </c>
       <c r="Q99">
-        <v>-5.767075227999999</v>
+        <v>-5.972640951999995</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.632047197222366</v>
+        <v>2.425170795833548</v>
       </c>
       <c r="T99">
-        <v>23.08182950301148</v>
+        <v>34.62274425451722</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0331873691501717</v>
+        <v>0.03284872252619037</v>
       </c>
       <c r="W99">
-        <v>0.2279744183543895</v>
+        <v>0.2280542712283243</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3687485461130189</v>
+        <v>0.3649858058465596</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2719966017204288</v>
+        <v>0.2738966017204288</v>
       </c>
       <c r="C100">
-        <v>-64.77964726151045</v>
+        <v>-65.92493751432838</v>
       </c>
       <c r="D100">
-        <v>22.48435273848954</v>
+        <v>22.29706248567161</v>
       </c>
       <c r="E100">
-        <v>40.38399999999999</v>
+        <v>41.34199999999999</v>
       </c>
       <c r="F100">
-        <v>93.88399999999999</v>
+        <v>94.84199999999998</v>
       </c>
       <c r="G100">
         <v>6.62</v>
@@ -9475,37 +9475,37 @@
         <v>8.080000000000002</v>
       </c>
       <c r="M100">
-        <v>22.1378472</v>
+        <v>22.3637436</v>
       </c>
       <c r="N100">
-        <v>-14.05784719999999</v>
+        <v>-14.28374359999999</v>
       </c>
       <c r="O100">
-        <v>-1.265206247999999</v>
+        <v>-1.285536923999999</v>
       </c>
       <c r="P100">
-        <v>-12.79264095199999</v>
+        <v>-12.998206676</v>
       </c>
       <c r="Q100">
-        <v>-5.972640951999995</v>
+        <v>-6.178206675999996</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.425170795833548</v>
+        <v>4.804541591667096</v>
       </c>
       <c r="T100">
-        <v>34.62274425451722</v>
+        <v>69.24548850903443</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03284872252619037</v>
+        <v>0.03251691724814804</v>
       </c>
       <c r="W100">
-        <v>0.2280542712283243</v>
+        <v>0.2281325109128867</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3649858058465596</v>
+        <v>0.3612990805349782</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2738966017204288</v>
-      </c>
-      <c r="C101">
-        <v>-65.92493751432838</v>
-      </c>
-      <c r="D101">
-        <v>22.29706248567161</v>
-      </c>
-      <c r="E101">
-        <v>41.34199999999999</v>
-      </c>
-      <c r="F101">
-        <v>94.84199999999998</v>
-      </c>
-      <c r="G101">
-        <v>6.62</v>
-      </c>
-      <c r="H101">
-        <v>42.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14.9</v>
-      </c>
-      <c r="K101">
-        <v>6.819999999999999</v>
-      </c>
-      <c r="L101">
-        <v>8.080000000000002</v>
-      </c>
-      <c r="M101">
-        <v>22.3637436</v>
-      </c>
-      <c r="N101">
-        <v>-14.28374359999999</v>
-      </c>
-      <c r="O101">
-        <v>-1.285536923999999</v>
-      </c>
-      <c r="P101">
-        <v>-12.998206676</v>
-      </c>
-      <c r="Q101">
-        <v>-6.178206675999996</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.804541591667096</v>
-      </c>
-      <c r="T101">
-        <v>69.24548850903443</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03251691724814804</v>
-      </c>
-      <c r="W101">
-        <v>0.2281325109128867</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3612990805349782</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
